--- a/research/traditional_assets/database/data/brazil/brazil_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.117498323043203</v>
+        <v>0.1171285287448561</v>
       </c>
       <c r="C2">
-        <v>34.04233274668995</v>
+        <v>33.81282443899054</v>
       </c>
       <c r="D2">
-        <v>29.99233274668995</v>
+        <v>30.14782443899054</v>
       </c>
       <c r="E2">
-        <v>-18.2</v>
+        <v>-17.815</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="G2">
         <v>4.05</v>
@@ -1451,28 +1451,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0193655</v>
       </c>
       <c r="N2">
-        <v>1.790333333333334</v>
+        <v>1.770967833333334</v>
       </c>
       <c r="O2">
-        <v>0.6087133333333334</v>
+        <v>0.6021290633333335</v>
       </c>
       <c r="P2">
-        <v>1.18162</v>
+        <v>1.16883877</v>
       </c>
       <c r="Q2">
-        <v>2.96462</v>
+        <v>2.95183877</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.117498323043203</v>
+        <v>0.117976311863491</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460948</v>
+        <v>0.9406993003370687</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>92.44963121702685</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1171285287448561</v>
+        <v>0.1167587344465092</v>
       </c>
       <c r="C3">
-        <v>33.81282443899054</v>
+        <v>33.58493678988099</v>
       </c>
       <c r="D3">
-        <v>30.14782443899054</v>
+        <v>30.30493678988099</v>
       </c>
       <c r="E3">
-        <v>-17.815</v>
+        <v>-17.43</v>
       </c>
       <c r="F3">
-        <v>0.385</v>
+        <v>0.77</v>
       </c>
       <c r="G3">
         <v>4.05</v>
@@ -1533,28 +1533,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M3">
-        <v>0.0193655</v>
+        <v>0.038731</v>
       </c>
       <c r="N3">
-        <v>1.770967833333334</v>
+        <v>1.751602333333333</v>
       </c>
       <c r="O3">
-        <v>0.6021290633333335</v>
+        <v>0.5955447933333334</v>
       </c>
       <c r="P3">
-        <v>1.16883877</v>
+        <v>1.15605754</v>
       </c>
       <c r="Q3">
-        <v>2.95183877</v>
+        <v>2.93905754</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.117976311863491</v>
+        <v>0.1184640555576624</v>
       </c>
       <c r="T3">
-        <v>0.9406993003370687</v>
+        <v>0.9470562357360217</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>92.44963121702685</v>
+        <v>46.22481560851342</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1167587344465092</v>
+        <v>0.1163889401481623</v>
       </c>
       <c r="C4">
-        <v>33.58493678988099</v>
+        <v>33.35869526979496</v>
       </c>
       <c r="D4">
-        <v>30.30493678988099</v>
+        <v>30.46369526979496</v>
       </c>
       <c r="E4">
-        <v>-17.43</v>
+        <v>-17.045</v>
       </c>
       <c r="F4">
-        <v>0.77</v>
+        <v>1.155</v>
       </c>
       <c r="G4">
         <v>4.05</v>
@@ -1615,28 +1615,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M4">
-        <v>0.038731</v>
+        <v>0.0580965</v>
       </c>
       <c r="N4">
-        <v>1.751602333333333</v>
+        <v>1.732236833333334</v>
       </c>
       <c r="O4">
-        <v>0.5955447933333334</v>
+        <v>0.5889605233333335</v>
       </c>
       <c r="P4">
-        <v>1.15605754</v>
+        <v>1.14327631</v>
       </c>
       <c r="Q4">
-        <v>2.93905754</v>
+        <v>2.92627631</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1184640555576624</v>
+        <v>0.1189618558228477</v>
       </c>
       <c r="T4">
-        <v>0.9470562357360217</v>
+        <v>0.9535442419679431</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.22481560851342</v>
+        <v>30.81654373900895</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1163889401481623</v>
+        <v>0.1160191458498154</v>
       </c>
       <c r="C5">
-        <v>33.35869526979496</v>
+        <v>33.13412588570478</v>
       </c>
       <c r="D5">
-        <v>30.46369526979496</v>
+        <v>30.62412588570478</v>
       </c>
       <c r="E5">
-        <v>-17.045</v>
+        <v>-16.66</v>
       </c>
       <c r="F5">
-        <v>1.155</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
         <v>4.05</v>
@@ -1697,28 +1697,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M5">
-        <v>0.0580965</v>
+        <v>0.077462</v>
       </c>
       <c r="N5">
-        <v>1.732236833333334</v>
+        <v>1.712871333333334</v>
       </c>
       <c r="O5">
-        <v>0.5889605233333335</v>
+        <v>0.5823762533333334</v>
       </c>
       <c r="P5">
-        <v>1.14327631</v>
+        <v>1.13049508</v>
       </c>
       <c r="Q5">
-        <v>2.92627631</v>
+        <v>2.913495080000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1189618558228477</v>
+        <v>0.1194700269268911</v>
       </c>
       <c r="T5">
-        <v>0.9535442419679431</v>
+        <v>0.9601674149963625</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.81654373900895</v>
+        <v>23.11240780425672</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1160191458498154</v>
+        <v>0.1156493515514685</v>
       </c>
       <c r="C6">
-        <v>33.13412588570478</v>
+        <v>32.91125519532402</v>
       </c>
       <c r="D6">
-        <v>30.62412588570478</v>
+        <v>30.78625519532401</v>
       </c>
       <c r="E6">
-        <v>-16.66</v>
+        <v>-16.275</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.925</v>
       </c>
       <c r="G6">
         <v>4.05</v>
@@ -1779,28 +1779,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M6">
-        <v>0.077462</v>
+        <v>0.0968275</v>
       </c>
       <c r="N6">
-        <v>1.712871333333334</v>
+        <v>1.693505833333333</v>
       </c>
       <c r="O6">
-        <v>0.5823762533333334</v>
+        <v>0.5757919833333335</v>
       </c>
       <c r="P6">
-        <v>1.13049508</v>
+        <v>1.11771385</v>
       </c>
       <c r="Q6">
-        <v>2.913495080000001</v>
+        <v>2.90071385</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1194700269268911</v>
+        <v>0.1199888963699669</v>
       </c>
       <c r="T6">
-        <v>0.9601674149963625</v>
+        <v>0.9669300232464328</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.11240780425672</v>
+        <v>18.48992624340537</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1156493515514685</v>
+        <v>0.1152795572531216</v>
       </c>
       <c r="C7">
-        <v>32.91125519532402</v>
+        <v>32.6901103217637</v>
       </c>
       <c r="D7">
-        <v>30.78625519532401</v>
+        <v>30.9501103217637</v>
       </c>
       <c r="E7">
-        <v>-16.275</v>
+        <v>-15.89</v>
       </c>
       <c r="F7">
-        <v>1.925</v>
+        <v>2.31</v>
       </c>
       <c r="G7">
         <v>4.05</v>
@@ -1861,28 +1861,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M7">
-        <v>0.0968275</v>
+        <v>0.116193</v>
       </c>
       <c r="N7">
-        <v>1.693505833333333</v>
+        <v>1.674140333333334</v>
       </c>
       <c r="O7">
-        <v>0.5757919833333335</v>
+        <v>0.5692077133333334</v>
       </c>
       <c r="P7">
-        <v>1.11771385</v>
+        <v>1.10493262</v>
       </c>
       <c r="Q7">
-        <v>2.90071385</v>
+        <v>2.88793262</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1199888963699669</v>
+        <v>0.1205188055884273</v>
       </c>
       <c r="T7">
-        <v>0.9669300232464328</v>
+        <v>0.9738365167784198</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.48992624340537</v>
+        <v>15.40827186950448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1152795572531216</v>
+        <v>0.1149097629547747</v>
       </c>
       <c r="C8">
-        <v>32.6901103217637</v>
+        <v>32.470718968659</v>
       </c>
       <c r="D8">
-        <v>30.9501103217637</v>
+        <v>31.115718968659</v>
       </c>
       <c r="E8">
-        <v>-15.89</v>
+        <v>-15.505</v>
       </c>
       <c r="F8">
-        <v>2.31</v>
+        <v>2.695</v>
       </c>
       <c r="G8">
         <v>4.05</v>
@@ -1943,28 +1943,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M8">
-        <v>0.116193</v>
+        <v>0.1355585</v>
       </c>
       <c r="N8">
-        <v>1.674140333333334</v>
+        <v>1.654774833333334</v>
       </c>
       <c r="O8">
-        <v>0.5692077133333334</v>
+        <v>0.5626234433333335</v>
       </c>
       <c r="P8">
-        <v>1.10493262</v>
+        <v>1.09215139</v>
       </c>
       <c r="Q8">
-        <v>2.88793262</v>
+        <v>2.87515139</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1205188055884273</v>
+        <v>0.1210601107040589</v>
       </c>
       <c r="T8">
-        <v>0.9738365167784198</v>
+        <v>0.9808915370530298</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.40827186950448</v>
+        <v>13.20709017386098</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1149097629547748</v>
+        <v>0.1146191686564279</v>
       </c>
       <c r="C9">
-        <v>32.47071896865899</v>
+        <v>32.21710751487056</v>
       </c>
       <c r="D9">
-        <v>31.115718968659</v>
+        <v>31.24710751487056</v>
       </c>
       <c r="E9">
-        <v>-15.505</v>
+        <v>-15.12</v>
       </c>
       <c r="F9">
-        <v>2.695</v>
+        <v>3.08</v>
       </c>
       <c r="G9">
         <v>4.05</v>
@@ -2025,45 +2025,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M9">
-        <v>0.1355585</v>
+        <v>0.159544</v>
       </c>
       <c r="N9">
-        <v>1.654774833333334</v>
+        <v>1.630789333333334</v>
       </c>
       <c r="O9">
-        <v>0.5626234433333335</v>
+        <v>0.5544683733333334</v>
       </c>
       <c r="P9">
-        <v>1.09215139</v>
+        <v>1.07632096</v>
       </c>
       <c r="Q9">
-        <v>2.87515139</v>
+        <v>2.859320960000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1210601107040589</v>
+        <v>0.1216131833222042</v>
       </c>
       <c r="T9">
-        <v>0.98089153705303</v>
+        <v>0.9880999273336097</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.20709017386098</v>
+        <v>11.22156479299337</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1146191686564279</v>
+        <v>0.114259274358081</v>
       </c>
       <c r="C10">
-        <v>32.21710751487056</v>
+        <v>31.99637533599313</v>
       </c>
       <c r="D10">
-        <v>31.24710751487056</v>
+        <v>31.41137533599313</v>
       </c>
       <c r="E10">
-        <v>-15.12</v>
+        <v>-14.735</v>
       </c>
       <c r="F10">
-        <v>3.08</v>
+        <v>3.465</v>
       </c>
       <c r="G10">
         <v>4.05</v>
@@ -2107,28 +2107,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M10">
-        <v>0.159544</v>
+        <v>0.179487</v>
       </c>
       <c r="N10">
-        <v>1.630789333333334</v>
+        <v>1.610846333333334</v>
       </c>
       <c r="O10">
-        <v>0.5544683733333334</v>
+        <v>0.5476877533333334</v>
       </c>
       <c r="P10">
-        <v>1.07632096</v>
+        <v>1.06315858</v>
       </c>
       <c r="Q10">
-        <v>2.859320960000001</v>
+        <v>2.84615858</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1216131833222042</v>
+        <v>0.1221784113825066</v>
       </c>
       <c r="T10">
-        <v>0.9880999273336097</v>
+        <v>0.9954667437742025</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.22156479299337</v>
+        <v>9.974724260438549</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.114259274358081</v>
+        <v>0.1140115800597341</v>
       </c>
       <c r="C11">
-        <v>31.99637533599313</v>
+        <v>31.72543835237754</v>
       </c>
       <c r="D11">
-        <v>31.41137533599313</v>
+        <v>31.52543835237755</v>
       </c>
       <c r="E11">
-        <v>-14.735</v>
+        <v>-14.35</v>
       </c>
       <c r="F11">
-        <v>3.465</v>
+        <v>3.85</v>
       </c>
       <c r="G11">
         <v>4.05</v>
@@ -2189,45 +2189,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M11">
-        <v>0.179487</v>
+        <v>0.205975</v>
       </c>
       <c r="N11">
-        <v>1.610846333333334</v>
+        <v>1.584358333333334</v>
       </c>
       <c r="O11">
-        <v>0.5476877533333334</v>
+        <v>0.5386818333333334</v>
       </c>
       <c r="P11">
-        <v>1.06315858</v>
+        <v>1.0456765</v>
       </c>
       <c r="Q11">
-        <v>2.84615858</v>
+        <v>2.8286765</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1221784113825066</v>
+        <v>0.1227562000663712</v>
       </c>
       <c r="T11">
-        <v>0.9954667437742025</v>
+        <v>1.002997267246808</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.34</v>
       </c>
       <c r="W11">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.974724260438549</v>
+        <v>8.691993364890564</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1140115800597341</v>
+        <v>0.1136629057613872</v>
       </c>
       <c r="C12">
-        <v>31.72543835237754</v>
+        <v>31.50241358721707</v>
       </c>
       <c r="D12">
-        <v>31.52543835237754</v>
+        <v>31.68741358721707</v>
       </c>
       <c r="E12">
-        <v>-14.35</v>
+        <v>-13.965</v>
       </c>
       <c r="F12">
-        <v>3.85</v>
+        <v>4.235</v>
       </c>
       <c r="G12">
         <v>4.05</v>
@@ -2271,28 +2271,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M12">
-        <v>0.205975</v>
+        <v>0.2265725</v>
       </c>
       <c r="N12">
-        <v>1.584358333333334</v>
+        <v>1.563760833333333</v>
       </c>
       <c r="O12">
-        <v>0.5386818333333334</v>
+        <v>0.5316786833333335</v>
       </c>
       <c r="P12">
-        <v>1.0456765</v>
+        <v>1.03208215</v>
       </c>
       <c r="Q12">
-        <v>2.8286765</v>
+        <v>2.81508215</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1227562000663712</v>
+        <v>0.1233469727656036</v>
       </c>
       <c r="T12">
-        <v>1.002997267246808</v>
+        <v>1.01069701596599</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.691993364890562</v>
+        <v>7.90181214990051</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1136629057613872</v>
+        <v>0.1133775914630403</v>
       </c>
       <c r="C13">
-        <v>31.50241358721707</v>
+        <v>31.25119864789075</v>
       </c>
       <c r="D13">
-        <v>31.68741358721707</v>
+        <v>31.82119864789075</v>
       </c>
       <c r="E13">
-        <v>-13.965</v>
+        <v>-13.58</v>
       </c>
       <c r="F13">
-        <v>4.235</v>
+        <v>4.62</v>
       </c>
       <c r="G13">
         <v>4.05</v>
@@ -2353,45 +2353,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M13">
-        <v>0.2265725</v>
+        <v>0.250866</v>
       </c>
       <c r="N13">
-        <v>1.563760833333333</v>
+        <v>1.539467333333334</v>
       </c>
       <c r="O13">
-        <v>0.5316786833333335</v>
+        <v>0.5234188933333335</v>
       </c>
       <c r="P13">
-        <v>1.03208215</v>
+        <v>1.01604844</v>
       </c>
       <c r="Q13">
-        <v>2.81508215</v>
+        <v>2.79904844</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1233469727656036</v>
+        <v>0.1239511721170913</v>
       </c>
       <c r="T13">
-        <v>1.01069701596599</v>
+        <v>1.018571758974243</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.90181214990051</v>
+        <v>7.1366121089878</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1133775914630403</v>
+        <v>0.1130341971646934</v>
       </c>
       <c r="C14">
-        <v>31.25119864789075</v>
+        <v>31.02872335470747</v>
       </c>
       <c r="D14">
-        <v>31.82119864789075</v>
+        <v>31.98372335470747</v>
       </c>
       <c r="E14">
-        <v>-13.58</v>
+        <v>-13.195</v>
       </c>
       <c r="F14">
-        <v>4.62</v>
+        <v>5.005</v>
       </c>
       <c r="G14">
         <v>4.05</v>
@@ -2435,28 +2435,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M14">
-        <v>0.250866</v>
+        <v>0.2717715</v>
       </c>
       <c r="N14">
-        <v>1.539467333333334</v>
+        <v>1.518561833333333</v>
       </c>
       <c r="O14">
-        <v>0.5234188933333335</v>
+        <v>0.5163110233333335</v>
       </c>
       <c r="P14">
-        <v>1.01604844</v>
+        <v>1.00225081</v>
       </c>
       <c r="Q14">
-        <v>2.79904844</v>
+        <v>2.78525081</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1239511721170913</v>
+        <v>0.124569261108843</v>
       </c>
       <c r="T14">
-        <v>1.018571758974243</v>
+        <v>1.026627530557399</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.1366121089878</v>
+        <v>6.587641946757969</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1130341971646934</v>
+        <v>0.1126908028663465</v>
       </c>
       <c r="C15">
-        <v>31.02872335470747</v>
+        <v>30.80791675304141</v>
       </c>
       <c r="D15">
-        <v>31.98372335470747</v>
+        <v>32.14791675304141</v>
       </c>
       <c r="E15">
-        <v>-13.195</v>
+        <v>-12.81</v>
       </c>
       <c r="F15">
-        <v>5.005</v>
+        <v>5.390000000000001</v>
       </c>
       <c r="G15">
         <v>4.05</v>
@@ -2517,28 +2517,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M15">
-        <v>0.2717715</v>
+        <v>0.292677</v>
       </c>
       <c r="N15">
-        <v>1.518561833333333</v>
+        <v>1.497656333333333</v>
       </c>
       <c r="O15">
-        <v>0.5163110233333335</v>
+        <v>0.5092031533333334</v>
       </c>
       <c r="P15">
-        <v>1.00225081</v>
+        <v>0.98845318</v>
       </c>
       <c r="Q15">
-        <v>2.78525081</v>
+        <v>2.77145318</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.124569261108843</v>
+        <v>0.1252017242631936</v>
       </c>
       <c r="T15">
-        <v>1.026627530557399</v>
+        <v>1.034870645665745</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.587641946757969</v>
+        <v>6.117096093418114</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1126908028663465</v>
+        <v>0.1124464085679996</v>
       </c>
       <c r="C16">
-        <v>30.80791675304141</v>
+        <v>30.54080408901327</v>
       </c>
       <c r="D16">
-        <v>32.14791675304141</v>
+        <v>32.26580408901327</v>
       </c>
       <c r="E16">
-        <v>-12.81</v>
+        <v>-12.425</v>
       </c>
       <c r="F16">
-        <v>5.390000000000001</v>
+        <v>5.775000000000001</v>
       </c>
       <c r="G16">
         <v>4.05</v>
@@ -2599,45 +2599,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M16">
-        <v>0.292677</v>
+        <v>0.3193575000000001</v>
       </c>
       <c r="N16">
-        <v>1.497656333333333</v>
+        <v>1.470975833333334</v>
       </c>
       <c r="O16">
-        <v>0.5092031533333334</v>
+        <v>0.5001317833333334</v>
       </c>
       <c r="P16">
-        <v>0.98845318</v>
+        <v>0.9708440500000002</v>
       </c>
       <c r="Q16">
-        <v>2.77145318</v>
+        <v>2.753844050000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1252017242631936</v>
+        <v>0.125849068903529</v>
       </c>
       <c r="T16">
-        <v>1.034870645665745</v>
+        <v>1.043307716423699</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.117096093418114</v>
+        <v>5.606047559031284</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1124464085679996</v>
+        <v>0.1121096142696527</v>
       </c>
       <c r="C17">
-        <v>30.54080408901327</v>
+        <v>30.31968588757972</v>
       </c>
       <c r="D17">
-        <v>32.26580408901327</v>
+        <v>32.42968588757972</v>
       </c>
       <c r="E17">
-        <v>-12.425</v>
+        <v>-12.04</v>
       </c>
       <c r="F17">
-        <v>5.774999999999999</v>
+        <v>6.16</v>
       </c>
       <c r="G17">
         <v>4.05</v>
@@ -2681,28 +2681,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M17">
-        <v>0.3193575</v>
+        <v>0.340648</v>
       </c>
       <c r="N17">
-        <v>1.470975833333334</v>
+        <v>1.449685333333333</v>
       </c>
       <c r="O17">
-        <v>0.5001317833333334</v>
+        <v>0.4928930133333334</v>
       </c>
       <c r="P17">
-        <v>0.9708440500000002</v>
+        <v>0.9567923200000001</v>
       </c>
       <c r="Q17">
-        <v>2.753844050000001</v>
+        <v>2.73979232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.125849068903529</v>
+        <v>0.1265118265114913</v>
       </c>
       <c r="T17">
-        <v>1.043307716423699</v>
+        <v>1.051945669818747</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.606047559031285</v>
+        <v>5.255669586591829</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1121096142696527</v>
+        <v>0.1117728199713058</v>
       </c>
       <c r="C18">
-        <v>30.31968588757972</v>
+        <v>30.10024093447429</v>
       </c>
       <c r="D18">
-        <v>32.42968588757972</v>
+        <v>32.5952409344743</v>
       </c>
       <c r="E18">
-        <v>-12.04</v>
+        <v>-11.655</v>
       </c>
       <c r="F18">
-        <v>6.16</v>
+        <v>6.545000000000001</v>
       </c>
       <c r="G18">
         <v>4.05</v>
@@ -2763,28 +2763,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M18">
-        <v>0.340648</v>
+        <v>0.3619385000000001</v>
       </c>
       <c r="N18">
-        <v>1.449685333333333</v>
+        <v>1.428394833333333</v>
       </c>
       <c r="O18">
-        <v>0.4928930133333334</v>
+        <v>0.4856542433333334</v>
       </c>
       <c r="P18">
-        <v>0.9567923200000001</v>
+        <v>0.94274059</v>
       </c>
       <c r="Q18">
-        <v>2.73979232</v>
+        <v>2.72574059</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1265118265114913</v>
+        <v>0.1271905541822962</v>
       </c>
       <c r="T18">
-        <v>1.051945669818747</v>
+        <v>1.060791766669097</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.255669586591829</v>
+        <v>4.946512552086427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1117728199713058</v>
+        <v>0.1114360256729589</v>
       </c>
       <c r="C19">
-        <v>30.10024093447429</v>
+        <v>29.88249498722078</v>
       </c>
       <c r="D19">
-        <v>32.5952409344743</v>
+        <v>32.76249498722078</v>
       </c>
       <c r="E19">
-        <v>-11.655</v>
+        <v>-11.27</v>
       </c>
       <c r="F19">
-        <v>6.545000000000001</v>
+        <v>6.930000000000001</v>
       </c>
       <c r="G19">
         <v>4.05</v>
@@ -2845,28 +2845,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M19">
-        <v>0.3619385000000001</v>
+        <v>0.383229</v>
       </c>
       <c r="N19">
-        <v>1.428394833333333</v>
+        <v>1.407104333333334</v>
       </c>
       <c r="O19">
-        <v>0.4856542433333334</v>
+        <v>0.4784154733333335</v>
       </c>
       <c r="P19">
-        <v>0.94274059</v>
+        <v>0.9286888600000001</v>
       </c>
       <c r="Q19">
-        <v>2.72574059</v>
+        <v>2.71168886</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1271905541822962</v>
+        <v>0.1278858361865353</v>
       </c>
       <c r="T19">
-        <v>1.060791766669097</v>
+        <v>1.069853621979212</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.946512552086427</v>
+        <v>4.671706299192737</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1114360256729589</v>
+        <v>0.1114127313746121</v>
       </c>
       <c r="C20">
-        <v>29.88249498722077</v>
+        <v>29.50912656110638</v>
       </c>
       <c r="D20">
-        <v>32.76249498722078</v>
+        <v>32.77412656110639</v>
       </c>
       <c r="E20">
-        <v>-11.27</v>
+        <v>-10.885</v>
       </c>
       <c r="F20">
-        <v>6.93</v>
+        <v>7.315</v>
       </c>
       <c r="G20">
         <v>4.05</v>
@@ -2927,45 +2927,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M20">
-        <v>0.383229</v>
+        <v>0.422807</v>
       </c>
       <c r="N20">
-        <v>1.407104333333334</v>
+        <v>1.367526333333334</v>
       </c>
       <c r="O20">
-        <v>0.4784154733333335</v>
+        <v>0.4649589533333335</v>
       </c>
       <c r="P20">
-        <v>0.9286888600000001</v>
+        <v>0.9025673800000001</v>
       </c>
       <c r="Q20">
-        <v>2.71168886</v>
+        <v>2.68556738</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1278858361865353</v>
+        <v>0.1285982856476692</v>
       </c>
       <c r="T20">
-        <v>1.069853621979212</v>
+        <v>1.079139226803157</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.671706299192738</v>
+        <v>4.234398515950146</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1114127313746121</v>
+        <v>0.1110924370762652</v>
       </c>
       <c r="C21">
-        <v>29.50912656110638</v>
+        <v>29.28490116749088</v>
       </c>
       <c r="D21">
-        <v>32.77412656110639</v>
+        <v>32.93490116749089</v>
       </c>
       <c r="E21">
-        <v>-10.885</v>
+        <v>-10.5</v>
       </c>
       <c r="F21">
-        <v>7.315</v>
+        <v>7.7</v>
       </c>
       <c r="G21">
         <v>4.05</v>
@@ -3009,28 +3009,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M21">
-        <v>0.422807</v>
+        <v>0.4450600000000001</v>
       </c>
       <c r="N21">
-        <v>1.367526333333334</v>
+        <v>1.345273333333334</v>
       </c>
       <c r="O21">
-        <v>0.4649589533333335</v>
+        <v>0.4573929333333334</v>
       </c>
       <c r="P21">
-        <v>0.9025673800000001</v>
+        <v>0.8878804000000001</v>
       </c>
       <c r="Q21">
-        <v>2.68556738</v>
+        <v>2.6708804</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1285982856476692</v>
+        <v>0.1293285463453315</v>
       </c>
       <c r="T21">
-        <v>1.079139226803157</v>
+        <v>1.088656971747701</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.234398515950146</v>
+        <v>4.022678590152639</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1110924370762652</v>
+        <v>0.1112572427779183</v>
       </c>
       <c r="C22">
-        <v>29.28490116749088</v>
+        <v>28.8169789534557</v>
       </c>
       <c r="D22">
-        <v>32.93490116749089</v>
+        <v>32.8519789534557</v>
       </c>
       <c r="E22">
-        <v>-10.5</v>
+        <v>-10.115</v>
       </c>
       <c r="F22">
-        <v>7.7</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="G22">
         <v>4.05</v>
@@ -3091,45 +3091,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M22">
-        <v>0.4450600000000001</v>
+        <v>0.4956105000000001</v>
       </c>
       <c r="N22">
-        <v>1.345273333333334</v>
+        <v>1.294722833333334</v>
       </c>
       <c r="O22">
-        <v>0.4573929333333334</v>
+        <v>0.4402057633333334</v>
       </c>
       <c r="P22">
-        <v>0.8878804000000001</v>
+        <v>0.8545170700000002</v>
       </c>
       <c r="Q22">
-        <v>2.6708804</v>
+        <v>2.63751707</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1293285463453315</v>
+        <v>0.1300772946555928</v>
       </c>
       <c r="T22">
-        <v>1.088656971747701</v>
+        <v>1.09841567226046</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.022678590152639</v>
+        <v>3.61237974847856</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1112572427779183</v>
+        <v>0.1113666084795714</v>
       </c>
       <c r="C23">
-        <v>28.8169789534557</v>
+        <v>28.37718155257966</v>
       </c>
       <c r="D23">
-        <v>32.8519789534557</v>
+        <v>32.79718155257966</v>
       </c>
       <c r="E23">
-        <v>-10.115</v>
+        <v>-9.729999999999999</v>
       </c>
       <c r="F23">
-        <v>8.084999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G23">
         <v>4.05</v>
@@ -3173,45 +3173,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M23">
-        <v>0.4956105</v>
+        <v>0.542927</v>
       </c>
       <c r="N23">
-        <v>1.294722833333334</v>
+        <v>1.247406333333334</v>
       </c>
       <c r="O23">
-        <v>0.4402057633333334</v>
+        <v>0.4241181533333335</v>
       </c>
       <c r="P23">
-        <v>0.8545170700000002</v>
+        <v>0.8232881800000001</v>
       </c>
       <c r="Q23">
-        <v>2.63751707</v>
+        <v>2.60628818</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1300772946555928</v>
+        <v>0.1308452416404761</v>
       </c>
       <c r="T23">
-        <v>1.09841567226046</v>
+        <v>1.108424595863291</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.34</v>
       </c>
       <c r="W23">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.612379748478561</v>
+        <v>3.297558112477982</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1113666084795714</v>
+        <v>0.1110878941812245</v>
       </c>
       <c r="C24">
-        <v>28.37718155257966</v>
+        <v>28.13219286032392</v>
       </c>
       <c r="D24">
-        <v>32.79718155257966</v>
+        <v>32.93719286032393</v>
       </c>
       <c r="E24">
-        <v>-9.729999999999999</v>
+        <v>-9.344999999999999</v>
       </c>
       <c r="F24">
-        <v>8.470000000000001</v>
+        <v>8.855</v>
       </c>
       <c r="G24">
         <v>4.05</v>
@@ -3255,28 +3255,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M24">
-        <v>0.542927</v>
+        <v>0.5676055000000001</v>
       </c>
       <c r="N24">
-        <v>1.247406333333334</v>
+        <v>1.222727833333333</v>
       </c>
       <c r="O24">
-        <v>0.4241181533333335</v>
+        <v>0.4157274633333334</v>
       </c>
       <c r="P24">
-        <v>0.8232881800000001</v>
+        <v>0.8070003699999999</v>
       </c>
       <c r="Q24">
-        <v>2.60628818</v>
+        <v>2.59000037</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1308452416404761</v>
+        <v>0.1316331353002916</v>
       </c>
       <c r="T24">
-        <v>1.108424595863291</v>
+        <v>1.118693491507754</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.297558112477982</v>
+        <v>3.154186020631113</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1110878941812245</v>
+        <v>0.1108091798828776</v>
       </c>
       <c r="C25">
-        <v>28.13219286032392</v>
+        <v>27.88840471092902</v>
       </c>
       <c r="D25">
-        <v>32.93719286032393</v>
+        <v>33.07840471092902</v>
       </c>
       <c r="E25">
-        <v>-9.344999999999999</v>
+        <v>-8.959999999999999</v>
       </c>
       <c r="F25">
-        <v>8.855</v>
+        <v>9.24</v>
       </c>
       <c r="G25">
         <v>4.05</v>
@@ -3337,28 +3337,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M25">
-        <v>0.5676055000000001</v>
+        <v>0.592284</v>
       </c>
       <c r="N25">
-        <v>1.222727833333333</v>
+        <v>1.198049333333334</v>
       </c>
       <c r="O25">
-        <v>0.4157274633333334</v>
+        <v>0.4073367733333334</v>
       </c>
       <c r="P25">
-        <v>0.8070003699999999</v>
+        <v>0.7907125600000001</v>
       </c>
       <c r="Q25">
-        <v>2.59000037</v>
+        <v>2.57371256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1316331353002916</v>
+        <v>0.1324417630037864</v>
       </c>
       <c r="T25">
-        <v>1.118693491507754</v>
+        <v>1.129232621248123</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.154186020631113</v>
+        <v>3.022761603104817</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1108091798828776</v>
+        <v>0.1118174655845307</v>
       </c>
       <c r="C26">
-        <v>27.88840471092902</v>
+        <v>26.99819775988636</v>
       </c>
       <c r="D26">
-        <v>33.07840471092903</v>
+        <v>32.57319775988636</v>
       </c>
       <c r="E26">
-        <v>-8.959999999999999</v>
+        <v>-8.574999999999999</v>
       </c>
       <c r="F26">
-        <v>9.24</v>
+        <v>9.625</v>
       </c>
       <c r="G26">
         <v>4.05</v>
@@ -3419,45 +3419,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M26">
-        <v>0.592284</v>
+        <v>0.6920375000000001</v>
       </c>
       <c r="N26">
-        <v>1.198049333333334</v>
+        <v>1.098295833333333</v>
       </c>
       <c r="O26">
-        <v>0.4073367733333334</v>
+        <v>0.3734205833333334</v>
       </c>
       <c r="P26">
-        <v>0.7907125600000001</v>
+        <v>0.7248752500000001</v>
       </c>
       <c r="Q26">
-        <v>2.57371256</v>
+        <v>2.50787525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1324417630037863</v>
+        <v>0.1332719541127076</v>
       </c>
       <c r="T26">
-        <v>1.129232621248123</v>
+        <v>1.140052794448236</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.34</v>
       </c>
       <c r="W26">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.022761603104817</v>
+        <v>2.587046703875633</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1118174655845307</v>
+        <v>0.1122594712861838</v>
       </c>
       <c r="C27">
-        <v>26.99819775988636</v>
+        <v>26.3965613820713</v>
       </c>
       <c r="D27">
-        <v>32.57319775988636</v>
+        <v>32.3565613820713</v>
       </c>
       <c r="E27">
-        <v>-8.574999999999999</v>
+        <v>-8.19</v>
       </c>
       <c r="F27">
-        <v>9.625</v>
+        <v>10.01</v>
       </c>
       <c r="G27">
         <v>4.05</v>
@@ -3501,45 +3501,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M27">
-        <v>0.6920375000000001</v>
+        <v>0.758758</v>
       </c>
       <c r="N27">
-        <v>1.098295833333333</v>
+        <v>1.031575333333334</v>
       </c>
       <c r="O27">
-        <v>0.3734205833333334</v>
+        <v>0.3507356133333334</v>
       </c>
       <c r="P27">
-        <v>0.7248752500000001</v>
+        <v>0.68083972</v>
       </c>
       <c r="Q27">
-        <v>2.50787525</v>
+        <v>2.46383972</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1332719541127076</v>
+        <v>0.1341245828191673</v>
       </c>
       <c r="T27">
-        <v>1.140052794448236</v>
+        <v>1.151165404761865</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.34</v>
       </c>
       <c r="W27">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.587046703875633</v>
+        <v>2.359557768528745</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1122594712861838</v>
+        <v>0.1120579769878369</v>
       </c>
       <c r="C28">
-        <v>26.3965613820713</v>
+        <v>26.10995953621046</v>
       </c>
       <c r="D28">
-        <v>32.3565613820713</v>
+        <v>32.45495953621047</v>
       </c>
       <c r="E28">
-        <v>-8.19</v>
+        <v>-7.804999999999998</v>
       </c>
       <c r="F28">
-        <v>10.01</v>
+        <v>10.395</v>
       </c>
       <c r="G28">
         <v>4.05</v>
@@ -3583,28 +3583,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M28">
-        <v>0.758758</v>
+        <v>0.7879410000000001</v>
       </c>
       <c r="N28">
-        <v>1.031575333333334</v>
+        <v>1.002392333333333</v>
       </c>
       <c r="O28">
-        <v>0.3507356133333334</v>
+        <v>0.3408133933333334</v>
       </c>
       <c r="P28">
-        <v>0.68083972</v>
+        <v>0.6615789399999999</v>
       </c>
       <c r="Q28">
-        <v>2.46383972</v>
+        <v>2.44457894</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1341245828191673</v>
+        <v>0.135000571216215</v>
       </c>
       <c r="T28">
-        <v>1.151165404761865</v>
+        <v>1.16258247015258</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.359557768528745</v>
+        <v>2.272166740064717</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1120579769878369</v>
+        <v>0.11185648268949</v>
       </c>
       <c r="C29">
-        <v>26.10995953621046</v>
+        <v>25.82395798471045</v>
       </c>
       <c r="D29">
-        <v>32.45495953621047</v>
+        <v>32.55395798471045</v>
       </c>
       <c r="E29">
-        <v>-7.804999999999998</v>
+        <v>-7.419999999999998</v>
       </c>
       <c r="F29">
-        <v>10.395</v>
+        <v>10.78</v>
       </c>
       <c r="G29">
         <v>4.05</v>
@@ -3665,28 +3665,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M29">
-        <v>0.7879410000000001</v>
+        <v>0.8171240000000002</v>
       </c>
       <c r="N29">
-        <v>1.002392333333333</v>
+        <v>0.9732093333333334</v>
       </c>
       <c r="O29">
-        <v>0.3408133933333334</v>
+        <v>0.3308911733333333</v>
       </c>
       <c r="P29">
-        <v>0.6615789399999999</v>
+        <v>0.6423181600000001</v>
       </c>
       <c r="Q29">
-        <v>2.44457894</v>
+        <v>2.42531816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.135000571216215</v>
+        <v>0.1359008926242917</v>
       </c>
       <c r="T29">
-        <v>1.16258247015258</v>
+        <v>1.174316676248592</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.272166740064717</v>
+        <v>2.191017927919549</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.11185648268949</v>
+        <v>0.1116549883911432</v>
       </c>
       <c r="C30">
-        <v>25.82395798471045</v>
+        <v>25.53856223767279</v>
       </c>
       <c r="D30">
-        <v>32.55395798471045</v>
+        <v>32.65356223767279</v>
       </c>
       <c r="E30">
-        <v>-7.419999999999998</v>
+        <v>-7.034999999999998</v>
       </c>
       <c r="F30">
-        <v>10.78</v>
+        <v>11.165</v>
       </c>
       <c r="G30">
         <v>4.05</v>
@@ -3747,28 +3747,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M30">
-        <v>0.8171240000000002</v>
+        <v>0.8463070000000001</v>
       </c>
       <c r="N30">
-        <v>0.9732093333333334</v>
+        <v>0.9440263333333334</v>
       </c>
       <c r="O30">
-        <v>0.3308911733333333</v>
+        <v>0.3209689533333334</v>
       </c>
       <c r="P30">
-        <v>0.6423181600000001</v>
+        <v>0.6230573800000001</v>
       </c>
       <c r="Q30">
-        <v>2.42531816</v>
+        <v>2.40605738</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1359008926242917</v>
+        <v>0.1368265751987932</v>
       </c>
       <c r="T30">
-        <v>1.174316676248592</v>
+        <v>1.186381423361394</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.191017927919549</v>
+        <v>2.115465585577495</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1116549883911432</v>
+        <v>0.1114534940927963</v>
       </c>
       <c r="C31">
-        <v>25.53856223767279</v>
+        <v>25.25377787284229</v>
       </c>
       <c r="D31">
-        <v>32.65356223767279</v>
+        <v>32.75377787284229</v>
       </c>
       <c r="E31">
-        <v>-7.035</v>
+        <v>-6.65</v>
       </c>
       <c r="F31">
-        <v>11.165</v>
+        <v>11.55</v>
       </c>
       <c r="G31">
         <v>4.05</v>
@@ -3829,28 +3829,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M31">
-        <v>0.846307</v>
+        <v>0.87549</v>
       </c>
       <c r="N31">
-        <v>0.9440263333333335</v>
+        <v>0.9148433333333336</v>
       </c>
       <c r="O31">
-        <v>0.3209689533333334</v>
+        <v>0.3110467333333334</v>
       </c>
       <c r="P31">
-        <v>0.6230573800000001</v>
+        <v>0.6037966000000001</v>
       </c>
       <c r="Q31">
-        <v>2.40605738</v>
+        <v>2.3867966</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1368265751987932</v>
+        <v>0.1377787058468518</v>
       </c>
       <c r="T31">
-        <v>1.186381423361394</v>
+        <v>1.198790877534562</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.115465585577495</v>
+        <v>2.044950066058246</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1114534940927963</v>
+        <v>0.1141573197944494</v>
       </c>
       <c r="C32">
-        <v>25.25377787284229</v>
+        <v>23.57322522822237</v>
       </c>
       <c r="D32">
-        <v>32.75377787284229</v>
+        <v>31.45822522822237</v>
       </c>
       <c r="E32">
-        <v>-6.65</v>
+        <v>-6.264999999999999</v>
       </c>
       <c r="F32">
-        <v>11.55</v>
+        <v>11.935</v>
       </c>
       <c r="G32">
         <v>4.05</v>
@@ -3911,45 +3911,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M32">
-        <v>0.87549</v>
+        <v>1.07415</v>
       </c>
       <c r="N32">
-        <v>0.9148433333333336</v>
+        <v>0.7161833333333336</v>
       </c>
       <c r="O32">
-        <v>0.3110467333333334</v>
+        <v>0.2435023333333335</v>
       </c>
       <c r="P32">
-        <v>0.6037966000000001</v>
+        <v>0.4726810000000001</v>
       </c>
       <c r="Q32">
-        <v>2.3867966</v>
+        <v>2.255681</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1377787058468518</v>
+        <v>0.1387584344847093</v>
       </c>
       <c r="T32">
-        <v>1.198790877534562</v>
+        <v>1.211560026031589</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.044950066058246</v>
+        <v>1.666744247389409</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1141573197944494</v>
+        <v>0.1140495454961025</v>
       </c>
       <c r="C33">
-        <v>23.57322522822237</v>
+        <v>23.23790157590448</v>
       </c>
       <c r="D33">
-        <v>31.45822522822237</v>
+        <v>31.50790157590448</v>
       </c>
       <c r="E33">
-        <v>-6.264999999999999</v>
+        <v>-5.879999999999999</v>
       </c>
       <c r="F33">
-        <v>11.935</v>
+        <v>12.32</v>
       </c>
       <c r="G33">
         <v>4.05</v>
@@ -3993,28 +3993,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M33">
-        <v>1.07415</v>
+        <v>1.1088</v>
       </c>
       <c r="N33">
-        <v>0.7161833333333336</v>
+        <v>0.6815333333333335</v>
       </c>
       <c r="O33">
-        <v>0.2435023333333335</v>
+        <v>0.2317213333333334</v>
       </c>
       <c r="P33">
-        <v>0.4726810000000001</v>
+        <v>0.4498120000000001</v>
       </c>
       <c r="Q33">
-        <v>2.255681</v>
+        <v>2.232812</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1387584344847093</v>
+        <v>0.139766978670739</v>
       </c>
       <c r="T33">
-        <v>1.211560026031589</v>
+        <v>1.224704737719705</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.666744247389409</v>
+        <v>1.61465848965849</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1140495454961025</v>
+        <v>0.1139417711977556</v>
       </c>
       <c r="C34">
-        <v>23.23790157590448</v>
+        <v>22.90273506166567</v>
       </c>
       <c r="D34">
-        <v>31.50790157590448</v>
+        <v>31.55773506166567</v>
       </c>
       <c r="E34">
-        <v>-5.879999999999999</v>
+        <v>-5.494999999999999</v>
       </c>
       <c r="F34">
-        <v>12.32</v>
+        <v>12.705</v>
       </c>
       <c r="G34">
         <v>4.05</v>
@@ -4075,28 +4075,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M34">
-        <v>1.1088</v>
+        <v>1.14345</v>
       </c>
       <c r="N34">
-        <v>0.6815333333333335</v>
+        <v>0.6468833333333337</v>
       </c>
       <c r="O34">
-        <v>0.2317213333333334</v>
+        <v>0.2199403333333335</v>
       </c>
       <c r="P34">
-        <v>0.4498120000000001</v>
+        <v>0.4269430000000002</v>
       </c>
       <c r="Q34">
-        <v>2.232812</v>
+        <v>2.209943</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.139766978670739</v>
+        <v>0.1408056286533666</v>
       </c>
       <c r="T34">
-        <v>1.224704737719705</v>
+        <v>1.238241828861198</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.61465848965849</v>
+        <v>1.565729444517324</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1139417711977556</v>
+        <v>0.1138339968994087</v>
       </c>
       <c r="C35">
-        <v>22.90273506166567</v>
+        <v>22.56772643228463</v>
       </c>
       <c r="D35">
-        <v>31.55773506166567</v>
+        <v>31.60772643228464</v>
       </c>
       <c r="E35">
-        <v>-5.494999999999999</v>
+        <v>-5.109999999999998</v>
       </c>
       <c r="F35">
-        <v>12.705</v>
+        <v>13.09</v>
       </c>
       <c r="G35">
         <v>4.05</v>
@@ -4157,28 +4157,28 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M35">
-        <v>1.14345</v>
+        <v>1.1781</v>
       </c>
       <c r="N35">
-        <v>0.6468833333333337</v>
+        <v>0.6122333333333334</v>
       </c>
       <c r="O35">
-        <v>0.2199403333333335</v>
+        <v>0.2081593333333334</v>
       </c>
       <c r="P35">
-        <v>0.4269430000000002</v>
+        <v>0.404074</v>
       </c>
       <c r="Q35">
-        <v>2.209943</v>
+        <v>2.187074</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1408056286533666</v>
+        <v>0.141875752877892</v>
       </c>
       <c r="T35">
-        <v>1.238241828861198</v>
+        <v>1.252189134885767</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.565729444517324</v>
+        <v>1.519678578502108</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1138339968994087</v>
+        <v>0.1293154941130619</v>
       </c>
       <c r="C36">
-        <v>22.56772643228463</v>
+        <v>16.32351511002541</v>
       </c>
       <c r="D36">
-        <v>31.60772643228464</v>
+        <v>25.74851511002541</v>
       </c>
       <c r="E36">
-        <v>-5.109999999999998</v>
+        <v>-4.724999999999998</v>
       </c>
       <c r="F36">
-        <v>13.09</v>
+        <v>13.475</v>
       </c>
       <c r="G36">
         <v>4.05</v>
@@ -4239,45 +4239,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M36">
-        <v>1.1781</v>
+        <v>1.97813</v>
       </c>
       <c r="N36">
-        <v>0.6122333333333334</v>
+        <v>-0.1877966666666668</v>
       </c>
       <c r="O36">
-        <v>0.2081593333333334</v>
+        <v>-0.06385086666666673</v>
       </c>
       <c r="P36">
-        <v>0.404074</v>
+        <v>-0.1239458000000001</v>
       </c>
       <c r="Q36">
-        <v>2.187074</v>
+        <v>1.6590542</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.141875752877892</v>
+        <v>0.1442249692981505</v>
       </c>
       <c r="T36">
-        <v>1.252189134885767</v>
+        <v>1.282807300123375</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.34</v>
+        <v>0.307721602388788</v>
       </c>
       <c r="W36">
-        <v>0.05939999999999999</v>
+        <v>0.1016264687693259</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.519678578502108</v>
+        <v>0.9050635364376118</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1293154941130619</v>
+        <v>0.1303254941130619</v>
       </c>
       <c r="C37">
-        <v>16.32351511002541</v>
+        <v>15.63084461919882</v>
       </c>
       <c r="D37">
-        <v>25.74851511002541</v>
+        <v>25.44084461919882</v>
       </c>
       <c r="E37">
-        <v>-4.724999999999998</v>
+        <v>-4.339999999999998</v>
       </c>
       <c r="F37">
-        <v>13.475</v>
+        <v>13.86</v>
       </c>
       <c r="G37">
         <v>4.05</v>
@@ -4321,37 +4321,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M37">
-        <v>1.97813</v>
+        <v>2.034648</v>
       </c>
       <c r="N37">
-        <v>-0.1877966666666668</v>
+        <v>-0.2443146666666667</v>
       </c>
       <c r="O37">
-        <v>-0.06385086666666673</v>
+        <v>-0.08306698666666668</v>
       </c>
       <c r="P37">
-        <v>-0.1239458000000001</v>
+        <v>-0.16124768</v>
       </c>
       <c r="Q37">
-        <v>1.6590542</v>
+        <v>1.62175232</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1442249692981505</v>
+        <v>0.1457628594434341</v>
       </c>
       <c r="T37">
-        <v>1.282807300123375</v>
+        <v>1.302851164187803</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.307721602388788</v>
+        <v>0.2991737801002106</v>
       </c>
       <c r="W37">
-        <v>0.1016264687693259</v>
+        <v>0.1028812890812891</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9050635364376118</v>
+        <v>0.8799228826476783</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1303254941130619</v>
+        <v>0.1313354941130619</v>
       </c>
       <c r="C38">
-        <v>15.63084461919882</v>
+        <v>14.94544005227803</v>
       </c>
       <c r="D38">
-        <v>25.44084461919882</v>
+        <v>25.14044005227803</v>
       </c>
       <c r="E38">
-        <v>-4.34</v>
+        <v>-3.955</v>
       </c>
       <c r="F38">
-        <v>13.86</v>
+        <v>14.245</v>
       </c>
       <c r="G38">
         <v>4.05</v>
@@ -4403,37 +4403,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M38">
-        <v>2.034648</v>
+        <v>2.091166</v>
       </c>
       <c r="N38">
-        <v>-0.2443146666666667</v>
+        <v>-0.3008326666666667</v>
       </c>
       <c r="O38">
-        <v>-0.08306698666666668</v>
+        <v>-0.1022831066666667</v>
       </c>
       <c r="P38">
-        <v>-0.16124768</v>
+        <v>-0.19854956</v>
       </c>
       <c r="Q38">
-        <v>1.62175232</v>
+        <v>1.58445044</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1457628594434341</v>
+        <v>0.1473495714980917</v>
       </c>
       <c r="T38">
-        <v>1.302851164187803</v>
+        <v>1.323531341397133</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2991737801002106</v>
+        <v>0.2910880022596644</v>
       </c>
       <c r="W38">
-        <v>0.1028812890812891</v>
+        <v>0.1040682812682813</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8799228826476783</v>
+        <v>0.8561411831166599</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1313354941130619</v>
+        <v>0.1323454941130618</v>
       </c>
       <c r="C39">
-        <v>14.94544005227803</v>
+        <v>14.26704702571989</v>
       </c>
       <c r="D39">
-        <v>25.14044005227803</v>
+        <v>24.84704702571989</v>
       </c>
       <c r="E39">
-        <v>-3.955</v>
+        <v>-3.569999999999999</v>
       </c>
       <c r="F39">
-        <v>14.245</v>
+        <v>14.63</v>
       </c>
       <c r="G39">
         <v>4.05</v>
@@ -4485,37 +4485,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M39">
-        <v>2.091166</v>
+        <v>2.147684</v>
       </c>
       <c r="N39">
-        <v>-0.3008326666666667</v>
+        <v>-0.3573506666666668</v>
       </c>
       <c r="O39">
-        <v>-0.1022831066666667</v>
+        <v>-0.1214992266666667</v>
       </c>
       <c r="P39">
-        <v>-0.19854956</v>
+        <v>-0.2358514400000001</v>
       </c>
       <c r="Q39">
-        <v>1.58445044</v>
+        <v>1.54714856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1473495714980917</v>
+        <v>0.1489874678125771</v>
       </c>
       <c r="T39">
-        <v>1.323531341397133</v>
+        <v>1.344878621097087</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2910880022596644</v>
+        <v>0.2834277916738838</v>
       </c>
       <c r="W39">
-        <v>0.1040682812682813</v>
+        <v>0.1051928001822739</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8561411831166599</v>
+        <v>0.833611151982011</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1323454941130618</v>
+        <v>0.1333554941130619</v>
       </c>
       <c r="C40">
-        <v>14.26704702571989</v>
+        <v>13.59542289378853</v>
       </c>
       <c r="D40">
-        <v>24.84704702571989</v>
+        <v>24.56042289378853</v>
       </c>
       <c r="E40">
-        <v>-3.569999999999999</v>
+        <v>-3.184999999999999</v>
       </c>
       <c r="F40">
-        <v>14.63</v>
+        <v>15.015</v>
       </c>
       <c r="G40">
         <v>4.05</v>
@@ -4567,37 +4567,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M40">
-        <v>2.147684</v>
+        <v>2.204202</v>
       </c>
       <c r="N40">
-        <v>-0.3573506666666668</v>
+        <v>-0.4138686666666669</v>
       </c>
       <c r="O40">
-        <v>-0.1214992266666667</v>
+        <v>-0.1407153466666667</v>
       </c>
       <c r="P40">
-        <v>-0.2358514400000001</v>
+        <v>-0.2731533200000001</v>
       </c>
       <c r="Q40">
-        <v>1.54714856</v>
+        <v>1.50984668</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1489874678125771</v>
+        <v>0.1506790656455701</v>
       </c>
       <c r="T40">
-        <v>1.344878621097087</v>
+        <v>1.366925811606875</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2834277916738838</v>
+        <v>0.2761604124001945</v>
       </c>
       <c r="W40">
-        <v>0.1051928001822739</v>
+        <v>0.1062596514596515</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.833611151982011</v>
+        <v>0.8122365070593953</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1333554941130619</v>
+        <v>0.1580421525889975</v>
       </c>
       <c r="C41">
-        <v>13.59542289378853</v>
+        <v>7.808577348080933</v>
       </c>
       <c r="D41">
-        <v>24.56042289378853</v>
+        <v>19.15857734808093</v>
       </c>
       <c r="E41">
-        <v>-3.184999999999999</v>
+        <v>-2.799999999999999</v>
       </c>
       <c r="F41">
-        <v>15.015</v>
+        <v>15.4</v>
       </c>
       <c r="G41">
         <v>4.05</v>
@@ -4649,45 +4649,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M41">
-        <v>2.204202</v>
+        <v>3.09232</v>
       </c>
       <c r="N41">
-        <v>-0.4138686666666669</v>
+        <v>-1.301986666666666</v>
       </c>
       <c r="O41">
-        <v>-0.1407153466666667</v>
+        <v>-0.4426754666666666</v>
       </c>
       <c r="P41">
-        <v>-0.2731533200000001</v>
+        <v>-0.8593111999999998</v>
       </c>
       <c r="Q41">
-        <v>1.50984668</v>
+        <v>0.9236888000000003</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1506790656455701</v>
+        <v>0.1558881475328891</v>
       </c>
       <c r="T41">
-        <v>1.366925811606875</v>
+        <v>1.434817611011467</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.2761604124001945</v>
+        <v>0.1968468118866526</v>
       </c>
       <c r="W41">
-        <v>0.1062596514596515</v>
+        <v>0.1612731601731602</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8122365070593953</v>
+        <v>0.5789612114313311</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1580421525889975</v>
+        <v>0.1595921525889975</v>
       </c>
       <c r="C42">
-        <v>7.808577348080933</v>
+        <v>7.16261212144722</v>
       </c>
       <c r="D42">
-        <v>19.15857734808093</v>
+        <v>18.89761212144722</v>
       </c>
       <c r="E42">
-        <v>-2.799999999999999</v>
+        <v>-2.414999999999997</v>
       </c>
       <c r="F42">
-        <v>15.4</v>
+        <v>15.785</v>
       </c>
       <c r="G42">
         <v>4.05</v>
@@ -4731,37 +4731,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M42">
-        <v>3.09232</v>
+        <v>3.169628</v>
       </c>
       <c r="N42">
-        <v>-1.301986666666666</v>
+        <v>-1.379294666666667</v>
       </c>
       <c r="O42">
-        <v>-0.4426754666666666</v>
+        <v>-0.4689601866666667</v>
       </c>
       <c r="P42">
-        <v>-0.8593111999999998</v>
+        <v>-0.9103344800000001</v>
       </c>
       <c r="Q42">
-        <v>0.9236888000000003</v>
+        <v>0.8726655200000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1558881475328891</v>
+        <v>0.1577540483385313</v>
       </c>
       <c r="T42">
-        <v>1.434817611011467</v>
+        <v>1.459136553570983</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1968468118866526</v>
+        <v>0.1920456701333195</v>
       </c>
       <c r="W42">
-        <v>0.1612731601731602</v>
+        <v>0.1622372294372295</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5789612114313311</v>
+        <v>0.5648402062744693</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1595921525889975</v>
+        <v>0.1611421525889976</v>
       </c>
       <c r="C43">
-        <v>7.16261212144722</v>
+        <v>6.523660741741153</v>
       </c>
       <c r="D43">
-        <v>18.89761212144722</v>
+        <v>18.64366074174115</v>
       </c>
       <c r="E43">
-        <v>-2.414999999999997</v>
+        <v>-2.029999999999998</v>
       </c>
       <c r="F43">
-        <v>15.785</v>
+        <v>16.17</v>
       </c>
       <c r="G43">
         <v>4.05</v>
@@ -4813,37 +4813,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M43">
-        <v>3.169628</v>
+        <v>3.246936</v>
       </c>
       <c r="N43">
-        <v>-1.379294666666667</v>
+        <v>-1.456602666666667</v>
       </c>
       <c r="O43">
-        <v>-0.4689601866666667</v>
+        <v>-0.4952449066666667</v>
       </c>
       <c r="P43">
-        <v>-0.9103344800000001</v>
+        <v>-0.9613577600000001</v>
       </c>
       <c r="Q43">
-        <v>0.8726655200000001</v>
+        <v>0.8216422400000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1577540483385313</v>
+        <v>0.1596842905512646</v>
       </c>
       <c r="T43">
-        <v>1.459136553570983</v>
+        <v>1.48429408035669</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1920456701333195</v>
+        <v>0.1874731541777643</v>
       </c>
       <c r="W43">
-        <v>0.1622372294372295</v>
+        <v>0.1631553906411049</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5648402062744693</v>
+        <v>0.5513916299346009</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1611421525889975</v>
+        <v>0.1626921525889976</v>
       </c>
       <c r="C44">
-        <v>6.523660741741157</v>
+        <v>5.891444196321675</v>
       </c>
       <c r="D44">
-        <v>18.64366074174115</v>
+        <v>18.39644419632167</v>
       </c>
       <c r="E44">
-        <v>-2.030000000000001</v>
+        <v>-1.645</v>
       </c>
       <c r="F44">
-        <v>16.17</v>
+        <v>16.555</v>
       </c>
       <c r="G44">
         <v>4.05</v>
@@ -4895,37 +4895,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M44">
-        <v>3.246936</v>
+        <v>3.324244</v>
       </c>
       <c r="N44">
-        <v>-1.456602666666666</v>
+        <v>-1.533910666666667</v>
       </c>
       <c r="O44">
-        <v>-0.4952449066666665</v>
+        <v>-0.5215296266666667</v>
       </c>
       <c r="P44">
-        <v>-0.9613577599999997</v>
+        <v>-1.01238104</v>
       </c>
       <c r="Q44">
-        <v>0.8216422400000004</v>
+        <v>0.7706189600000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1596842905512646</v>
+        <v>0.1616822605609359</v>
       </c>
       <c r="T44">
-        <v>1.48429408035669</v>
+        <v>1.510334327380492</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1874731541777644</v>
+        <v>0.1831133133829326</v>
       </c>
       <c r="W44">
-        <v>0.1631553906411049</v>
+        <v>0.1640308466727071</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.551391629934601</v>
+        <v>0.5385685687733311</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1626921525889976</v>
+        <v>0.1642421525889975</v>
       </c>
       <c r="C45">
-        <v>5.891444196321675</v>
+        <v>5.265698077807212</v>
       </c>
       <c r="D45">
-        <v>18.39644419632167</v>
+        <v>18.15569807780721</v>
       </c>
       <c r="E45">
-        <v>-1.645</v>
+        <v>-1.259999999999998</v>
       </c>
       <c r="F45">
-        <v>16.555</v>
+        <v>16.94</v>
       </c>
       <c r="G45">
         <v>4.05</v>
@@ -4977,37 +4977,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M45">
-        <v>3.324244</v>
+        <v>3.401552000000001</v>
       </c>
       <c r="N45">
-        <v>-1.533910666666667</v>
+        <v>-1.611218666666667</v>
       </c>
       <c r="O45">
-        <v>-0.5215296266666667</v>
+        <v>-0.5478143466666668</v>
       </c>
       <c r="P45">
-        <v>-1.01238104</v>
+        <v>-1.06340432</v>
       </c>
       <c r="Q45">
-        <v>0.7706189600000002</v>
+        <v>0.7195956800000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1616822605609359</v>
+        <v>0.1637515866423812</v>
       </c>
       <c r="T45">
-        <v>1.510334327380492</v>
+        <v>1.537304583226572</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1831133133829326</v>
+        <v>0.1789516471696841</v>
       </c>
       <c r="W45">
-        <v>0.1640308466727071</v>
+        <v>0.1648665092483274</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5385685687733311</v>
+        <v>0.5263283740284826</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1642421525889975</v>
+        <v>0.1657921525889975</v>
       </c>
       <c r="C46">
-        <v>5.265698077807212</v>
+        <v>4.646171640757693</v>
       </c>
       <c r="D46">
-        <v>18.15569807780721</v>
+        <v>17.92117164075769</v>
       </c>
       <c r="E46">
-        <v>-1.259999999999998</v>
+        <v>-0.875</v>
       </c>
       <c r="F46">
-        <v>16.94</v>
+        <v>17.325</v>
       </c>
       <c r="G46">
         <v>4.05</v>
@@ -5059,37 +5059,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M46">
-        <v>3.401552000000001</v>
+        <v>3.47886</v>
       </c>
       <c r="N46">
-        <v>-1.611218666666667</v>
+        <v>-1.688526666666667</v>
       </c>
       <c r="O46">
-        <v>-0.5478143466666668</v>
+        <v>-0.5740990666666667</v>
       </c>
       <c r="P46">
-        <v>-1.06340432</v>
+        <v>-1.1144276</v>
       </c>
       <c r="Q46">
-        <v>0.7195956800000001</v>
+        <v>0.6685724000000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1637515866423812</v>
+        <v>0.1658961609449699</v>
       </c>
       <c r="T46">
-        <v>1.537304583226572</v>
+        <v>1.565255575648873</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1789516471696841</v>
+        <v>0.1749749438992467</v>
       </c>
       <c r="W46">
-        <v>0.1648665092483274</v>
+        <v>0.1656650312650313</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5263283740284826</v>
+        <v>0.5146321879389609</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1657921525889975</v>
+        <v>0.1673421525889975</v>
       </c>
       <c r="C47">
-        <v>4.646171640757693</v>
+        <v>4.03262693053599</v>
       </c>
       <c r="D47">
-        <v>17.92117164075769</v>
+        <v>17.69262693053599</v>
       </c>
       <c r="E47">
-        <v>-0.875</v>
+        <v>-0.4899999999999984</v>
       </c>
       <c r="F47">
-        <v>17.325</v>
+        <v>17.71</v>
       </c>
       <c r="G47">
         <v>4.05</v>
@@ -5141,37 +5141,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M47">
-        <v>3.47886</v>
+        <v>3.556168</v>
       </c>
       <c r="N47">
-        <v>-1.688526666666667</v>
+        <v>-1.765834666666667</v>
       </c>
       <c r="O47">
-        <v>-0.5740990666666667</v>
+        <v>-0.6003837866666668</v>
       </c>
       <c r="P47">
-        <v>-1.1144276</v>
+        <v>-1.16545088</v>
       </c>
       <c r="Q47">
-        <v>0.6685724000000002</v>
+        <v>0.6175491200000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1658961609449699</v>
+        <v>0.1681201639254323</v>
       </c>
       <c r="T47">
-        <v>1.565255575648873</v>
+        <v>1.594241790012741</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1749749438992467</v>
+        <v>0.1711711407710022</v>
       </c>
       <c r="W47">
-        <v>0.1656650312650313</v>
+        <v>0.1664288349331828</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5146321879389609</v>
+        <v>0.5034445316794183</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1673421525889975</v>
+        <v>0.1861801093672903</v>
       </c>
       <c r="C48">
-        <v>4.03262693053599</v>
+        <v>1.273409223240513</v>
       </c>
       <c r="D48">
-        <v>17.69262693053599</v>
+        <v>15.31840922324051</v>
       </c>
       <c r="E48">
-        <v>-0.4899999999999984</v>
+        <v>-0.1049999999999969</v>
       </c>
       <c r="F48">
-        <v>17.71</v>
+        <v>18.095</v>
       </c>
       <c r="G48">
         <v>4.05</v>
@@ -5223,45 +5223,45 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M48">
-        <v>3.556168</v>
+        <v>4.266801000000001</v>
       </c>
       <c r="N48">
-        <v>-1.765834666666667</v>
+        <v>-2.476467666666667</v>
       </c>
       <c r="O48">
-        <v>-0.6003837866666668</v>
+        <v>-0.8419990066666669</v>
       </c>
       <c r="P48">
-        <v>-1.16545088</v>
+        <v>-1.63446866</v>
       </c>
       <c r="Q48">
-        <v>0.6175491200000001</v>
+        <v>0.1485313399999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1681201639254323</v>
+        <v>0.1720091420717476</v>
       </c>
       <c r="T48">
-        <v>1.594241790012741</v>
+        <v>1.644928212286354</v>
       </c>
       <c r="U48">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1711711407710022</v>
+        <v>0.1426626958541852</v>
       </c>
       <c r="W48">
-        <v>0.1664288349331828</v>
+        <v>0.2021601363175831</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5034445316794183</v>
+        <v>0.4195961642770154</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1861801093672903</v>
+        <v>0.1880801093672903</v>
       </c>
       <c r="C49">
-        <v>1.273409223240513</v>
+        <v>0.6838481102811222</v>
       </c>
       <c r="D49">
-        <v>15.31840922324051</v>
+        <v>15.11384811028112</v>
       </c>
       <c r="E49">
-        <v>-0.1049999999999969</v>
+        <v>0.2800000000000011</v>
       </c>
       <c r="F49">
-        <v>18.095</v>
+        <v>18.48</v>
       </c>
       <c r="G49">
         <v>4.05</v>
@@ -5305,37 +5305,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M49">
-        <v>4.266801000000001</v>
+        <v>4.357584</v>
       </c>
       <c r="N49">
-        <v>-2.476467666666667</v>
+        <v>-2.567250666666666</v>
       </c>
       <c r="O49">
-        <v>-0.8419990066666669</v>
+        <v>-0.8728652266666667</v>
       </c>
       <c r="P49">
-        <v>-1.63446866</v>
+        <v>-1.69438544</v>
       </c>
       <c r="Q49">
-        <v>0.1485313399999999</v>
+        <v>0.08861456000000056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1720091420717476</v>
+        <v>0.1744362409577427</v>
       </c>
       <c r="T49">
-        <v>1.644928212286354</v>
+        <v>1.676561447138015</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1426626958541852</v>
+        <v>0.1396905563572231</v>
       </c>
       <c r="W49">
-        <v>0.2021601363175831</v>
+        <v>0.2028609668109668</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4195961642770154</v>
+        <v>0.4108545775212443</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1880801093672903</v>
+        <v>0.1899801093672903</v>
       </c>
       <c r="C50">
-        <v>0.6838481102811222</v>
+        <v>0.09967839446144211</v>
       </c>
       <c r="D50">
-        <v>15.11384811028112</v>
+        <v>14.91467839446144</v>
       </c>
       <c r="E50">
-        <v>0.2800000000000011</v>
+        <v>0.6649999999999991</v>
       </c>
       <c r="F50">
-        <v>18.48</v>
+        <v>18.865</v>
       </c>
       <c r="G50">
         <v>4.05</v>
@@ -5387,37 +5387,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M50">
-        <v>4.357584</v>
+        <v>4.448367</v>
       </c>
       <c r="N50">
-        <v>-2.567250666666666</v>
+        <v>-2.658033666666666</v>
       </c>
       <c r="O50">
-        <v>-0.8728652266666667</v>
+        <v>-0.9037314466666666</v>
       </c>
       <c r="P50">
-        <v>-1.69438544</v>
+        <v>-1.75430222</v>
       </c>
       <c r="Q50">
-        <v>0.08861456000000056</v>
+        <v>0.02869778000000034</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1744362409577427</v>
+        <v>0.1769585201922083</v>
       </c>
       <c r="T50">
-        <v>1.676561447138015</v>
+        <v>1.709435201003466</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1396905563572231</v>
+        <v>0.1368397286764634</v>
       </c>
       <c r="W50">
-        <v>0.2028609668109668</v>
+        <v>0.2035331919780899</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4108545775212443</v>
+        <v>0.4024697902248924</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1899801093672903</v>
+        <v>0.1918801093672903</v>
       </c>
       <c r="C51">
-        <v>0.09967839446144211</v>
+        <v>-0.4793102948420902</v>
       </c>
       <c r="D51">
-        <v>14.91467839446144</v>
+        <v>14.72068970515791</v>
       </c>
       <c r="E51">
-        <v>0.6649999999999991</v>
+        <v>1.050000000000001</v>
       </c>
       <c r="F51">
-        <v>18.865</v>
+        <v>19.25</v>
       </c>
       <c r="G51">
         <v>4.05</v>
@@ -5469,37 +5469,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M51">
-        <v>4.448367</v>
+        <v>4.53915</v>
       </c>
       <c r="N51">
-        <v>-2.658033666666666</v>
+        <v>-2.748816666666666</v>
       </c>
       <c r="O51">
-        <v>-0.9037314466666666</v>
+        <v>-0.9345976666666667</v>
       </c>
       <c r="P51">
-        <v>-1.75430222</v>
+        <v>-1.814219</v>
       </c>
       <c r="Q51">
-        <v>0.02869778000000034</v>
+        <v>-0.03121899999999966</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1769585201922083</v>
+        <v>0.1795816905960524</v>
       </c>
       <c r="T51">
-        <v>1.709435201003466</v>
+        <v>1.743623905023536</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1368397286764634</v>
+        <v>0.1341029341029341</v>
       </c>
       <c r="W51">
-        <v>0.2035331919780899</v>
+        <v>0.2041785281385282</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4024697902248924</v>
+        <v>0.3944203944203944</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1918801093672903</v>
+        <v>0.1937801093672903</v>
       </c>
       <c r="C52">
-        <v>-0.4793102948420902</v>
+        <v>-1.053317523985164</v>
       </c>
       <c r="D52">
-        <v>14.72068970515791</v>
+        <v>14.53168247601484</v>
       </c>
       <c r="E52">
-        <v>1.050000000000001</v>
+        <v>1.435000000000002</v>
       </c>
       <c r="F52">
-        <v>19.25</v>
+        <v>19.635</v>
       </c>
       <c r="G52">
         <v>4.05</v>
@@ -5551,37 +5551,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M52">
-        <v>4.53915</v>
+        <v>4.629933</v>
       </c>
       <c r="N52">
-        <v>-2.748816666666666</v>
+        <v>-2.839599666666667</v>
       </c>
       <c r="O52">
-        <v>-0.9345976666666667</v>
+        <v>-0.9654638866666667</v>
       </c>
       <c r="P52">
-        <v>-1.814219</v>
+        <v>-1.87413578</v>
       </c>
       <c r="Q52">
-        <v>-0.03121899999999966</v>
+        <v>-0.09113577999999967</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1795816905960524</v>
+        <v>0.1823119291796454</v>
       </c>
       <c r="T52">
-        <v>1.743623905023536</v>
+        <v>1.779208066350547</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1341029341029341</v>
+        <v>0.1314734648067982</v>
       </c>
       <c r="W52">
-        <v>0.2041785281385282</v>
+        <v>0.204798556998557</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3944203944203944</v>
+        <v>0.3866866611964652</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1937801093672903</v>
+        <v>0.1956801093672903</v>
       </c>
       <c r="C53">
-        <v>-1.053317523985164</v>
+        <v>-1.622532739873268</v>
       </c>
       <c r="D53">
-        <v>14.53168247601484</v>
+        <v>14.34746726012673</v>
       </c>
       <c r="E53">
-        <v>1.435000000000002</v>
+        <v>1.82</v>
       </c>
       <c r="F53">
-        <v>19.635</v>
+        <v>20.02</v>
       </c>
       <c r="G53">
         <v>4.05</v>
@@ -5633,37 +5633,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M53">
-        <v>4.629933</v>
+        <v>4.720716</v>
       </c>
       <c r="N53">
-        <v>-2.839599666666667</v>
+        <v>-2.930382666666667</v>
       </c>
       <c r="O53">
-        <v>-0.9654638866666667</v>
+        <v>-0.9963301066666667</v>
       </c>
       <c r="P53">
-        <v>-1.87413578</v>
+        <v>-1.93405256</v>
       </c>
       <c r="Q53">
-        <v>-0.09113577999999967</v>
+        <v>-0.1510525599999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1823119291796454</v>
+        <v>0.1851559277042213</v>
       </c>
       <c r="T53">
-        <v>1.779208066350547</v>
+        <v>1.816274901066184</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1314734648067982</v>
+        <v>0.1289451289451289</v>
       </c>
       <c r="W53">
-        <v>0.204798556998557</v>
+        <v>0.2053947385947386</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3866866611964652</v>
+        <v>0.3792503792503793</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1956801093672903</v>
+        <v>0.1975801093672903</v>
       </c>
       <c r="C54">
-        <v>-1.622532739873268</v>
+        <v>-2.187135903343613</v>
       </c>
       <c r="D54">
-        <v>14.34746726012673</v>
+        <v>14.16786409665639</v>
       </c>
       <c r="E54">
-        <v>1.82</v>
+        <v>2.205000000000002</v>
       </c>
       <c r="F54">
-        <v>20.02</v>
+        <v>20.405</v>
       </c>
       <c r="G54">
         <v>4.05</v>
@@ -5715,37 +5715,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M54">
-        <v>4.720716</v>
+        <v>4.811499</v>
       </c>
       <c r="N54">
-        <v>-2.930382666666667</v>
+        <v>-3.021165666666667</v>
       </c>
       <c r="O54">
-        <v>-0.9963301066666667</v>
+        <v>-1.027196326666667</v>
       </c>
       <c r="P54">
-        <v>-1.93405256</v>
+        <v>-1.99396934</v>
       </c>
       <c r="Q54">
-        <v>-0.1510525599999999</v>
+        <v>-0.2109693399999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1851559277042213</v>
+        <v>0.188120947442609</v>
       </c>
       <c r="T54">
-        <v>1.816274901066184</v>
+        <v>1.854919047897379</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1289451289451289</v>
+        <v>0.1265122019839001</v>
       </c>
       <c r="W54">
-        <v>0.2053947385947386</v>
+        <v>0.2059684227721963</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3792503792503793</v>
+        <v>0.3720947117173533</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1975801093672903</v>
+        <v>0.1994801093672903</v>
       </c>
       <c r="C55">
-        <v>-2.187135903343613</v>
+        <v>-2.747298075562746</v>
       </c>
       <c r="D55">
-        <v>14.16786409665639</v>
+        <v>13.99270192443726</v>
       </c>
       <c r="E55">
-        <v>2.205000000000002</v>
+        <v>2.590000000000003</v>
       </c>
       <c r="F55">
-        <v>20.405</v>
+        <v>20.79</v>
       </c>
       <c r="G55">
         <v>4.05</v>
@@ -5797,37 +5797,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M55">
-        <v>4.811499</v>
+        <v>4.902282</v>
       </c>
       <c r="N55">
-        <v>-3.021165666666667</v>
+        <v>-3.111948666666667</v>
       </c>
       <c r="O55">
-        <v>-1.027196326666667</v>
+        <v>-1.058062546666667</v>
       </c>
       <c r="P55">
-        <v>-1.99396934</v>
+        <v>-2.05388612</v>
       </c>
       <c r="Q55">
-        <v>-0.2109693399999997</v>
+        <v>-0.2708861199999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.188120947442609</v>
+        <v>0.1912148810826657</v>
       </c>
       <c r="T55">
-        <v>1.854919047897379</v>
+        <v>1.895243375025583</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1265122019839001</v>
+        <v>0.1241693834286427</v>
       </c>
       <c r="W55">
-        <v>0.2059684227721963</v>
+        <v>0.2065208593875261</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3720947117173533</v>
+        <v>0.3652040689077727</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1994801093672903</v>
+        <v>0.2013801093672903</v>
       </c>
       <c r="C56">
-        <v>-2.747298075562746</v>
+        <v>-3.303181961456321</v>
       </c>
       <c r="D56">
-        <v>13.99270192443726</v>
+        <v>13.82181803854368</v>
       </c>
       <c r="E56">
-        <v>2.590000000000003</v>
+        <v>2.975000000000001</v>
       </c>
       <c r="F56">
-        <v>20.79</v>
+        <v>21.175</v>
       </c>
       <c r="G56">
         <v>4.05</v>
@@ -5879,37 +5879,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M56">
-        <v>4.902282</v>
+        <v>4.993065000000001</v>
       </c>
       <c r="N56">
-        <v>-3.111948666666667</v>
+        <v>-3.202731666666667</v>
       </c>
       <c r="O56">
-        <v>-1.058062546666667</v>
+        <v>-1.088928766666667</v>
       </c>
       <c r="P56">
-        <v>-2.05388612</v>
+        <v>-2.1138029</v>
       </c>
       <c r="Q56">
-        <v>-0.2708861199999999</v>
+        <v>-0.3308028999999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1912148810826657</v>
+        <v>0.1944463228845027</v>
       </c>
       <c r="T56">
-        <v>1.895243375025583</v>
+        <v>1.937359894470595</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1241693834286427</v>
+        <v>0.1219117582753946</v>
       </c>
       <c r="W56">
-        <v>0.2065208593875261</v>
+        <v>0.207053207398662</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3652040689077727</v>
+        <v>0.3585639949276314</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2013801093672903</v>
+        <v>0.2032801093672903</v>
       </c>
       <c r="C57">
-        <v>-3.303181961456321</v>
+        <v>-3.854942413800075</v>
       </c>
       <c r="D57">
-        <v>13.82181803854368</v>
+        <v>13.65505758619993</v>
       </c>
       <c r="E57">
-        <v>2.975000000000001</v>
+        <v>3.360000000000003</v>
       </c>
       <c r="F57">
-        <v>21.175</v>
+        <v>21.56</v>
       </c>
       <c r="G57">
         <v>4.05</v>
@@ -5961,37 +5961,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M57">
-        <v>4.993065000000001</v>
+        <v>5.083848000000001</v>
       </c>
       <c r="N57">
-        <v>-3.202731666666667</v>
+        <v>-3.293514666666667</v>
       </c>
       <c r="O57">
-        <v>-1.088928766666667</v>
+        <v>-1.119794986666667</v>
       </c>
       <c r="P57">
-        <v>-2.1138029</v>
+        <v>-2.17371968</v>
       </c>
       <c r="Q57">
-        <v>-0.3308028999999999</v>
+        <v>-0.3907196799999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1944463228845027</v>
+        <v>0.1978246484046051</v>
       </c>
       <c r="T57">
-        <v>1.937359894470595</v>
+        <v>1.981390801163109</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1219117582753946</v>
+        <v>0.1197347625919055</v>
       </c>
       <c r="W57">
-        <v>0.207053207398662</v>
+        <v>0.2075665429808287</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3585639949276314</v>
+        <v>0.3521610664467808</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2032801093672903</v>
+        <v>0.2051801093672903</v>
       </c>
       <c r="C58">
-        <v>-3.854942413800075</v>
+        <v>-4.402726901254475</v>
       </c>
       <c r="D58">
-        <v>13.65505758619993</v>
+        <v>13.49227309874553</v>
       </c>
       <c r="E58">
-        <v>3.360000000000003</v>
+        <v>3.745000000000005</v>
       </c>
       <c r="F58">
-        <v>21.56</v>
+        <v>21.945</v>
       </c>
       <c r="G58">
         <v>4.05</v>
@@ -6043,37 +6043,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M58">
-        <v>5.083848000000001</v>
+        <v>5.174631000000002</v>
       </c>
       <c r="N58">
-        <v>-3.293514666666667</v>
+        <v>-3.384297666666668</v>
       </c>
       <c r="O58">
-        <v>-1.119794986666667</v>
+        <v>-1.150661206666667</v>
       </c>
       <c r="P58">
-        <v>-2.17371968</v>
+        <v>-2.23363646</v>
       </c>
       <c r="Q58">
-        <v>-0.3907196799999999</v>
+        <v>-0.4506364600000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1978246484046051</v>
+        <v>0.201360105344247</v>
       </c>
       <c r="T58">
-        <v>1.981390801163109</v>
+        <v>2.027469657004112</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1197347625919055</v>
+        <v>0.117634152721872</v>
       </c>
       <c r="W58">
-        <v>0.2075665429808287</v>
+        <v>0.2080618667881826</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3521610664467808</v>
+        <v>0.345982802123153</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2051801093672903</v>
+        <v>0.2070801093672903</v>
       </c>
       <c r="C59">
-        <v>-4.402726901254475</v>
+        <v>-4.946675943316666</v>
       </c>
       <c r="D59">
-        <v>13.49227309874553</v>
+        <v>13.33332405668333</v>
       </c>
       <c r="E59">
-        <v>3.745000000000005</v>
+        <v>4.130000000000003</v>
       </c>
       <c r="F59">
-        <v>21.945</v>
+        <v>22.33</v>
       </c>
       <c r="G59">
         <v>4.05</v>
@@ -6125,37 +6125,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M59">
-        <v>5.174631000000002</v>
+        <v>5.265414000000001</v>
       </c>
       <c r="N59">
-        <v>-3.384297666666668</v>
+        <v>-3.475080666666667</v>
       </c>
       <c r="O59">
-        <v>-1.150661206666667</v>
+        <v>-1.181527426666667</v>
       </c>
       <c r="P59">
-        <v>-2.23363646</v>
+        <v>-2.29355324</v>
       </c>
       <c r="Q59">
-        <v>-0.4506364600000003</v>
+        <v>-0.5105532399999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.201360105344247</v>
+        <v>0.2050639173762529</v>
       </c>
       <c r="T59">
-        <v>2.027469657004112</v>
+        <v>2.075742744075638</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.117634152721872</v>
+        <v>0.1156059776749432</v>
       </c>
       <c r="W59">
-        <v>0.2080618667881826</v>
+        <v>0.2085401104642484</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.345982802123153</v>
+        <v>0.3400175813968918</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2070801093672903</v>
+        <v>0.2089801093672903</v>
       </c>
       <c r="C60">
-        <v>-4.946675943316659</v>
+        <v>-5.486923514886044</v>
       </c>
       <c r="D60">
-        <v>13.33332405668334</v>
+        <v>13.17807648511396</v>
       </c>
       <c r="E60">
-        <v>4.129999999999999</v>
+        <v>4.515000000000001</v>
       </c>
       <c r="F60">
-        <v>22.33</v>
+        <v>22.715</v>
       </c>
       <c r="G60">
         <v>4.05</v>
@@ -6207,37 +6207,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M60">
-        <v>5.265414</v>
+        <v>5.356197</v>
       </c>
       <c r="N60">
-        <v>-3.475080666666666</v>
+        <v>-3.565863666666666</v>
       </c>
       <c r="O60">
-        <v>-1.181527426666666</v>
+        <v>-1.212393646666666</v>
       </c>
       <c r="P60">
-        <v>-2.29355324</v>
+        <v>-2.35347002</v>
       </c>
       <c r="Q60">
-        <v>-0.5105532399999995</v>
+        <v>-0.5704700199999995</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2050639173762529</v>
+        <v>0.2089484031659176</v>
       </c>
       <c r="T60">
-        <v>2.075742744075638</v>
+        <v>2.126370615882361</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1156059776749432</v>
+        <v>0.1136465543245204</v>
       </c>
       <c r="W60">
-        <v>0.2085401104642484</v>
+        <v>0.2090021424902781</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3400175813968919</v>
+        <v>0.3342545715427072</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2089801093672903</v>
+        <v>0.2108801093672903</v>
       </c>
       <c r="C61">
-        <v>-5.486923514886044</v>
+        <v>-6.023597422891569</v>
       </c>
       <c r="D61">
-        <v>13.17807648511396</v>
+        <v>13.02640257710843</v>
       </c>
       <c r="E61">
-        <v>4.515000000000001</v>
+        <v>4.899999999999999</v>
       </c>
       <c r="F61">
-        <v>22.715</v>
+        <v>23.1</v>
       </c>
       <c r="G61">
         <v>4.05</v>
@@ -6289,37 +6289,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M61">
-        <v>5.356197</v>
+        <v>5.44698</v>
       </c>
       <c r="N61">
-        <v>-3.565863666666666</v>
+        <v>-3.656646666666666</v>
       </c>
       <c r="O61">
-        <v>-1.212393646666666</v>
+        <v>-1.243259866666667</v>
       </c>
       <c r="P61">
-        <v>-2.35347002</v>
+        <v>-2.4133868</v>
       </c>
       <c r="Q61">
-        <v>-0.5704700199999995</v>
+        <v>-0.6303867999999995</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2089484031659176</v>
+        <v>0.2130271132450655</v>
       </c>
       <c r="T61">
-        <v>2.126370615882361</v>
+        <v>2.17952988127942</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1136465543245204</v>
+        <v>0.1117524450857784</v>
       </c>
       <c r="W61">
-        <v>0.2090021424902781</v>
+        <v>0.2094487734487735</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3342545715427072</v>
+        <v>0.3286836620169954</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2108801093672903</v>
+        <v>0.2127801093672903</v>
       </c>
       <c r="C62">
-        <v>-6.023597422891569</v>
+        <v>-6.556819657206109</v>
       </c>
       <c r="D62">
-        <v>13.02640257710843</v>
+        <v>12.87818034279389</v>
       </c>
       <c r="E62">
-        <v>4.899999999999999</v>
+        <v>5.285</v>
       </c>
       <c r="F62">
-        <v>23.1</v>
+        <v>23.485</v>
       </c>
       <c r="G62">
         <v>4.05</v>
@@ -6371,37 +6371,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M62">
-        <v>5.44698</v>
+        <v>5.537763</v>
       </c>
       <c r="N62">
-        <v>-3.656646666666666</v>
+        <v>-3.747429666666666</v>
       </c>
       <c r="O62">
-        <v>-1.243259866666667</v>
+        <v>-1.274126086666667</v>
       </c>
       <c r="P62">
-        <v>-2.4133868</v>
+        <v>-2.47330358</v>
       </c>
       <c r="Q62">
-        <v>-0.6303867999999995</v>
+        <v>-0.6903035799999995</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2130271132450655</v>
+        <v>0.217314987943657</v>
       </c>
       <c r="T62">
-        <v>2.17952988127942</v>
+        <v>2.235415262850687</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1117524450857784</v>
+        <v>0.1099204377892903</v>
       </c>
       <c r="W62">
-        <v>0.2094487734487735</v>
+        <v>0.2098807607692854</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3286836620169954</v>
+        <v>0.3232954052626185</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2127801093672903</v>
+        <v>0.2146801093672903</v>
       </c>
       <c r="C63">
-        <v>-6.556819657206109</v>
+        <v>-7.086706717872879</v>
       </c>
       <c r="D63">
-        <v>12.87818034279389</v>
+        <v>12.73329328212712</v>
       </c>
       <c r="E63">
-        <v>5.285</v>
+        <v>5.670000000000002</v>
       </c>
       <c r="F63">
-        <v>23.485</v>
+        <v>23.87</v>
       </c>
       <c r="G63">
         <v>4.05</v>
@@ -6453,37 +6453,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M63">
-        <v>5.537763</v>
+        <v>5.628546</v>
       </c>
       <c r="N63">
-        <v>-3.747429666666666</v>
+        <v>-3.838212666666666</v>
       </c>
       <c r="O63">
-        <v>-1.274126086666667</v>
+        <v>-1.304992306666667</v>
       </c>
       <c r="P63">
-        <v>-2.47330358</v>
+        <v>-2.53322036</v>
       </c>
       <c r="Q63">
-        <v>-0.6903035799999995</v>
+        <v>-0.7502203599999995</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.217314987943657</v>
+        <v>0.2218285402579638</v>
       </c>
       <c r="T63">
-        <v>2.235415262850687</v>
+        <v>2.294241980294126</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1099204377892903</v>
+        <v>0.1081475275023662</v>
       </c>
       <c r="W63">
-        <v>0.2098807607692854</v>
+        <v>0.210298813014942</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3232954052626185</v>
+        <v>0.3180809632422537</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2146801093672903</v>
+        <v>0.2165801093672903</v>
       </c>
       <c r="C64">
-        <v>-7.086706717872879</v>
+        <v>-7.613369920488644</v>
       </c>
       <c r="D64">
-        <v>12.73329328212712</v>
+        <v>12.59163007951136</v>
       </c>
       <c r="E64">
-        <v>5.670000000000002</v>
+        <v>6.055</v>
       </c>
       <c r="F64">
-        <v>23.87</v>
+        <v>24.255</v>
       </c>
       <c r="G64">
         <v>4.05</v>
@@ -6535,37 +6535,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M64">
-        <v>5.628546</v>
+        <v>5.719329</v>
       </c>
       <c r="N64">
-        <v>-3.838212666666666</v>
+        <v>-3.928995666666666</v>
       </c>
       <c r="O64">
-        <v>-1.304992306666667</v>
+        <v>-1.335858526666667</v>
       </c>
       <c r="P64">
-        <v>-2.53322036</v>
+        <v>-2.59313714</v>
       </c>
       <c r="Q64">
-        <v>-0.7502203599999995</v>
+        <v>-0.8101371399999995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2218285402579638</v>
+        <v>0.2265860683730438</v>
       </c>
       <c r="T64">
-        <v>2.294241980294126</v>
+        <v>2.356248520302076</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1081475275023662</v>
+        <v>0.1064309000816937</v>
       </c>
       <c r="W64">
-        <v>0.210298813014942</v>
+        <v>0.2107035937607366</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3180809632422537</v>
+        <v>0.3130320590638052</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2165801093672903</v>
+        <v>0.2184801093672903</v>
       </c>
       <c r="C65">
-        <v>-7.613369920488644</v>
+        <v>-8.136915681426203</v>
       </c>
       <c r="D65">
-        <v>12.59163007951136</v>
+        <v>12.4530843185738</v>
       </c>
       <c r="E65">
-        <v>6.055</v>
+        <v>6.440000000000001</v>
       </c>
       <c r="F65">
-        <v>24.255</v>
+        <v>24.64</v>
       </c>
       <c r="G65">
         <v>4.05</v>
@@ -6617,37 +6617,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M65">
-        <v>5.719329</v>
+        <v>5.810112</v>
       </c>
       <c r="N65">
-        <v>-3.928995666666666</v>
+        <v>-4.019778666666666</v>
       </c>
       <c r="O65">
-        <v>-1.335858526666667</v>
+        <v>-1.366724746666667</v>
       </c>
       <c r="P65">
-        <v>-2.59313714</v>
+        <v>-2.65305392</v>
       </c>
       <c r="Q65">
-        <v>-0.8101371399999995</v>
+        <v>-0.8700539199999995</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2265860683730438</v>
+        <v>0.2316079036056284</v>
       </c>
       <c r="T65">
-        <v>2.356248520302076</v>
+        <v>2.421699868088244</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1064309000816937</v>
+        <v>0.1047679172679173</v>
       </c>
       <c r="W65">
-        <v>0.2107035937607366</v>
+        <v>0.2110957251082251</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3130320590638052</v>
+        <v>0.3081409331409332</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2184801093672903</v>
+        <v>0.2203801093672903</v>
       </c>
       <c r="C66">
-        <v>-8.136915681426203</v>
+        <v>-8.657445784431872</v>
       </c>
       <c r="D66">
-        <v>12.4530843185738</v>
+        <v>12.31755421556813</v>
       </c>
       <c r="E66">
-        <v>6.440000000000001</v>
+        <v>6.825000000000003</v>
       </c>
       <c r="F66">
-        <v>24.64</v>
+        <v>25.025</v>
       </c>
       <c r="G66">
         <v>4.05</v>
@@ -6699,37 +6699,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M66">
-        <v>5.810112</v>
+        <v>5.900895000000001</v>
       </c>
       <c r="N66">
-        <v>-4.019778666666666</v>
+        <v>-4.110561666666667</v>
       </c>
       <c r="O66">
-        <v>-1.366724746666667</v>
+        <v>-1.397590966666667</v>
       </c>
       <c r="P66">
-        <v>-2.65305392</v>
+        <v>-2.712970700000001</v>
       </c>
       <c r="Q66">
-        <v>-0.8700539199999995</v>
+        <v>-0.9299707000000004</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2316079036056284</v>
+        <v>0.2369167008515035</v>
       </c>
       <c r="T66">
-        <v>2.421699868088244</v>
+        <v>2.490891292890766</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1047679172679173</v>
+        <v>0.1031561031561032</v>
       </c>
       <c r="W66">
-        <v>0.2110957251082251</v>
+        <v>0.2114757908757909</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3081409331409332</v>
+        <v>0.3034003034003034</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2203801093672903</v>
+        <v>0.2222801093672903</v>
       </c>
       <c r="C67">
-        <v>-8.657445784431872</v>
+        <v>-9.175057630001799</v>
       </c>
       <c r="D67">
-        <v>12.31755421556813</v>
+        <v>12.1849423699982</v>
       </c>
       <c r="E67">
-        <v>6.825000000000003</v>
+        <v>7.210000000000001</v>
       </c>
       <c r="F67">
-        <v>25.025</v>
+        <v>25.41</v>
       </c>
       <c r="G67">
         <v>4.05</v>
@@ -6781,37 +6781,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M67">
-        <v>5.900895000000001</v>
+        <v>5.991678</v>
       </c>
       <c r="N67">
-        <v>-4.110561666666667</v>
+        <v>-4.201344666666667</v>
       </c>
       <c r="O67">
-        <v>-1.397590966666667</v>
+        <v>-1.428457186666667</v>
       </c>
       <c r="P67">
-        <v>-2.712970700000001</v>
+        <v>-2.77288748</v>
       </c>
       <c r="Q67">
-        <v>-0.9299707000000004</v>
+        <v>-0.9898874799999995</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2369167008515035</v>
+        <v>0.2425377802883124</v>
       </c>
       <c r="T67">
-        <v>2.490891292890766</v>
+        <v>2.5641528015052</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1031561031561032</v>
+        <v>0.1015931318961622</v>
       </c>
       <c r="W67">
-        <v>0.2114757908757909</v>
+        <v>0.211844339498885</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3034003034003034</v>
+        <v>0.2988033291063594</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2222801093672903</v>
+        <v>0.2241801093672903</v>
       </c>
       <c r="C68">
-        <v>-9.175057630001799</v>
+        <v>-9.689844468820962</v>
       </c>
       <c r="D68">
-        <v>12.1849423699982</v>
+        <v>12.05515553117904</v>
       </c>
       <c r="E68">
-        <v>7.210000000000001</v>
+        <v>7.595000000000002</v>
       </c>
       <c r="F68">
-        <v>25.41</v>
+        <v>25.795</v>
       </c>
       <c r="G68">
         <v>4.05</v>
@@ -6863,37 +6863,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M68">
-        <v>5.991678</v>
+        <v>6.082461</v>
       </c>
       <c r="N68">
-        <v>-4.201344666666667</v>
+        <v>-4.292127666666667</v>
       </c>
       <c r="O68">
-        <v>-1.428457186666667</v>
+        <v>-1.459323406666667</v>
       </c>
       <c r="P68">
-        <v>-2.77288748</v>
+        <v>-2.83280426</v>
       </c>
       <c r="Q68">
-        <v>-0.9898874799999995</v>
+        <v>-1.049804259999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2425377802883124</v>
+        <v>0.2484995312061401</v>
       </c>
       <c r="T68">
-        <v>2.5641528015052</v>
+        <v>2.641854401550812</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1015931318961622</v>
+        <v>0.100076816494727</v>
       </c>
       <c r="W68">
-        <v>0.211844339498885</v>
+        <v>0.2122018866705434</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2988033291063594</v>
+        <v>0.2943435779256676</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2241801093672903</v>
+        <v>0.2260801093672903</v>
       </c>
       <c r="C69">
-        <v>-9.689844468820962</v>
+        <v>-10.20189562044067</v>
       </c>
       <c r="D69">
-        <v>12.05515553117904</v>
+        <v>11.92810437955934</v>
       </c>
       <c r="E69">
-        <v>7.595000000000002</v>
+        <v>7.980000000000004</v>
       </c>
       <c r="F69">
-        <v>25.795</v>
+        <v>26.18</v>
       </c>
       <c r="G69">
         <v>4.05</v>
@@ -6945,37 +6945,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M69">
-        <v>6.082461</v>
+        <v>6.173244000000001</v>
       </c>
       <c r="N69">
-        <v>-4.292127666666667</v>
+        <v>-4.382910666666668</v>
       </c>
       <c r="O69">
-        <v>-1.459323406666667</v>
+        <v>-1.490189626666667</v>
       </c>
       <c r="P69">
-        <v>-2.83280426</v>
+        <v>-2.892721040000001</v>
       </c>
       <c r="Q69">
-        <v>-1.049804259999999</v>
+        <v>-1.10972104</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2484995312061401</v>
+        <v>0.254833891556332</v>
       </c>
       <c r="T69">
-        <v>2.641854401550812</v>
+        <v>2.724412351599275</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.100076816494727</v>
+        <v>0.0986050986050986</v>
       </c>
       <c r="W69">
-        <v>0.2122018866705434</v>
+        <v>0.2125489177489178</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2943435779256676</v>
+        <v>0.2900149958973488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2260801093672903</v>
+        <v>0.2279801093672903</v>
       </c>
       <c r="C70">
-        <v>-10.20189562044067</v>
+        <v>-10.71129667827224</v>
       </c>
       <c r="D70">
-        <v>11.92810437955934</v>
+        <v>11.80370332172776</v>
       </c>
       <c r="E70">
-        <v>7.980000000000004</v>
+        <v>8.365000000000002</v>
       </c>
       <c r="F70">
-        <v>26.18</v>
+        <v>26.565</v>
       </c>
       <c r="G70">
         <v>4.05</v>
@@ -7027,37 +7027,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M70">
-        <v>6.173244000000001</v>
+        <v>6.264027</v>
       </c>
       <c r="N70">
-        <v>-4.382910666666668</v>
+        <v>-4.473693666666667</v>
       </c>
       <c r="O70">
-        <v>-1.490189626666667</v>
+        <v>-1.521055846666667</v>
       </c>
       <c r="P70">
-        <v>-2.892721040000001</v>
+        <v>-2.95263782</v>
       </c>
       <c r="Q70">
-        <v>-1.10972104</v>
+        <v>-1.169637819999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.254833891556332</v>
+        <v>0.2615769203162137</v>
       </c>
       <c r="T70">
-        <v>2.724412351599275</v>
+        <v>2.812296621005704</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0986050986050986</v>
+        <v>0.09717603920502473</v>
       </c>
       <c r="W70">
-        <v>0.2125489177489178</v>
+        <v>0.2128858899554552</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2900149958973488</v>
+        <v>0.2858118800147786</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2279801093672903</v>
+        <v>0.2298801093672903</v>
       </c>
       <c r="C71">
-        <v>-10.71129667827224</v>
+        <v>-11.21812970188553</v>
       </c>
       <c r="D71">
-        <v>11.80370332172776</v>
+        <v>11.68187029811447</v>
       </c>
       <c r="E71">
-        <v>8.365000000000002</v>
+        <v>8.750000000000004</v>
       </c>
       <c r="F71">
-        <v>26.565</v>
+        <v>26.95</v>
       </c>
       <c r="G71">
         <v>4.05</v>
@@ -7109,37 +7109,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M71">
-        <v>6.264027</v>
+        <v>6.354810000000001</v>
       </c>
       <c r="N71">
-        <v>-4.473693666666667</v>
+        <v>-4.564476666666667</v>
       </c>
       <c r="O71">
-        <v>-1.521055846666667</v>
+        <v>-1.551922066666667</v>
       </c>
       <c r="P71">
-        <v>-2.95263782</v>
+        <v>-3.0125546</v>
       </c>
       <c r="Q71">
-        <v>-1.169637819999999</v>
+        <v>-1.229554599999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2615769203162137</v>
+        <v>0.2687694843267541</v>
       </c>
       <c r="T71">
-        <v>2.812296621005704</v>
+        <v>2.906039841705894</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09717603920502473</v>
+        <v>0.09578781007352437</v>
       </c>
       <c r="W71">
-        <v>0.2128858899554552</v>
+        <v>0.213213234384663</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2858118800147786</v>
+        <v>0.2817288531574247</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2298801093672903</v>
+        <v>0.2317801093672903</v>
       </c>
       <c r="C72">
-        <v>-11.21812970188553</v>
+        <v>-11.72247339752013</v>
       </c>
       <c r="D72">
-        <v>11.68187029811447</v>
+        <v>11.56252660247988</v>
       </c>
       <c r="E72">
-        <v>8.750000000000004</v>
+        <v>9.135000000000005</v>
       </c>
       <c r="F72">
-        <v>26.95</v>
+        <v>27.335</v>
       </c>
       <c r="G72">
         <v>4.05</v>
@@ -7191,37 +7191,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M72">
-        <v>6.354810000000001</v>
+        <v>6.445593000000001</v>
       </c>
       <c r="N72">
-        <v>-4.564476666666667</v>
+        <v>-4.655259666666668</v>
       </c>
       <c r="O72">
-        <v>-1.551922066666667</v>
+        <v>-1.582788286666667</v>
       </c>
       <c r="P72">
-        <v>-3.0125546</v>
+        <v>-3.072471380000001</v>
       </c>
       <c r="Q72">
-        <v>-1.229554599999999</v>
+        <v>-1.28947138</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2687694843267541</v>
+        <v>0.2764580872345732</v>
       </c>
       <c r="T72">
-        <v>2.906039841705894</v>
+        <v>3.006248112109545</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09578781007352437</v>
+        <v>0.09443868598798176</v>
       </c>
       <c r="W72">
-        <v>0.213213234384663</v>
+        <v>0.2135313578440339</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2817288531574247</v>
+        <v>0.2777608411411229</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2317801093672903</v>
+        <v>0.2336801093672903</v>
       </c>
       <c r="C73">
-        <v>-11.72247339752012</v>
+        <v>-12.22440328764364</v>
       </c>
       <c r="D73">
-        <v>11.56252660247988</v>
+        <v>11.44559671235636</v>
       </c>
       <c r="E73">
-        <v>9.134999999999998</v>
+        <v>9.52</v>
       </c>
       <c r="F73">
-        <v>27.335</v>
+        <v>27.72</v>
       </c>
       <c r="G73">
         <v>4.05</v>
@@ -7273,37 +7273,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M73">
-        <v>6.445593</v>
+        <v>6.536376</v>
       </c>
       <c r="N73">
-        <v>-4.655259666666666</v>
+        <v>-4.746042666666666</v>
       </c>
       <c r="O73">
-        <v>-1.582788286666666</v>
+        <v>-1.613654506666667</v>
       </c>
       <c r="P73">
-        <v>-3.07247138</v>
+        <v>-3.13238816</v>
       </c>
       <c r="Q73">
-        <v>-1.28947138</v>
+        <v>-1.34938816</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2764580872345732</v>
+        <v>0.2846958760643793</v>
       </c>
       <c r="T73">
-        <v>3.006248112109545</v>
+        <v>3.113614116113457</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09443868598798179</v>
+        <v>0.09312703757148204</v>
       </c>
       <c r="W73">
-        <v>0.2135313578440339</v>
+        <v>0.2138406445406446</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2777608411411229</v>
+        <v>0.2739030516808295</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2336801093672903</v>
+        <v>0.2355801093672903</v>
       </c>
       <c r="C74">
-        <v>-12.22440328764364</v>
+        <v>-12.72399187032482</v>
       </c>
       <c r="D74">
-        <v>11.44559671235636</v>
+        <v>11.33100812967518</v>
       </c>
       <c r="E74">
-        <v>9.52</v>
+        <v>9.905000000000001</v>
       </c>
       <c r="F74">
-        <v>27.72</v>
+        <v>28.105</v>
       </c>
       <c r="G74">
         <v>4.05</v>
@@ -7355,37 +7355,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M74">
-        <v>6.536376</v>
+        <v>6.627159000000001</v>
       </c>
       <c r="N74">
-        <v>-4.746042666666666</v>
+        <v>-4.836825666666667</v>
       </c>
       <c r="O74">
-        <v>-1.613654506666667</v>
+        <v>-1.644520726666667</v>
       </c>
       <c r="P74">
-        <v>-3.13238816</v>
+        <v>-3.19230494</v>
       </c>
       <c r="Q74">
-        <v>-1.34938816</v>
+        <v>-1.40930494</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2846958760643793</v>
+        <v>0.2935438714741712</v>
       </c>
       <c r="T74">
-        <v>3.113614116113457</v>
+        <v>3.228933157450992</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09312703757148204</v>
+        <v>0.09185132472803707</v>
       </c>
       <c r="W74">
-        <v>0.2138406445406446</v>
+        <v>0.2141414576291289</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2739030516808295</v>
+        <v>0.270150955082462</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2355801093672903</v>
+        <v>0.2374801093672903</v>
       </c>
       <c r="C75">
-        <v>-12.72399187032482</v>
+        <v>-13.22130876912797</v>
       </c>
       <c r="D75">
-        <v>11.33100812967518</v>
+        <v>11.21869123087203</v>
       </c>
       <c r="E75">
-        <v>9.905000000000001</v>
+        <v>10.29</v>
       </c>
       <c r="F75">
-        <v>28.105</v>
+        <v>28.49</v>
       </c>
       <c r="G75">
         <v>4.05</v>
@@ -7437,37 +7437,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M75">
-        <v>6.627159000000001</v>
+        <v>6.717942</v>
       </c>
       <c r="N75">
-        <v>-4.836825666666667</v>
+        <v>-4.927608666666666</v>
       </c>
       <c r="O75">
-        <v>-1.644520726666667</v>
+        <v>-1.675386946666667</v>
       </c>
       <c r="P75">
-        <v>-3.19230494</v>
+        <v>-3.25222172</v>
       </c>
       <c r="Q75">
-        <v>-1.40930494</v>
+        <v>-1.46922172</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2935438714741712</v>
+        <v>0.3030724819154855</v>
       </c>
       <c r="T75">
-        <v>3.228933157450992</v>
+        <v>3.35312289427603</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09185132472803707</v>
+        <v>0.09061009061009064</v>
       </c>
       <c r="W75">
-        <v>0.2141414576291289</v>
+        <v>0.2144341406341407</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.270150955082462</v>
+        <v>0.2665002665002666</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2374801093672903</v>
+        <v>0.2393801093672903</v>
       </c>
       <c r="C76">
-        <v>-13.22130876912797</v>
+        <v>-13.71642087418012</v>
       </c>
       <c r="D76">
-        <v>11.21869123087203</v>
+        <v>11.10857912581988</v>
       </c>
       <c r="E76">
-        <v>10.29</v>
+        <v>10.675</v>
       </c>
       <c r="F76">
-        <v>28.49</v>
+        <v>28.875</v>
       </c>
       <c r="G76">
         <v>4.05</v>
@@ -7519,37 +7519,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M76">
-        <v>6.717942</v>
+        <v>6.808725</v>
       </c>
       <c r="N76">
-        <v>-4.927608666666666</v>
+        <v>-5.018391666666666</v>
       </c>
       <c r="O76">
-        <v>-1.675386946666667</v>
+        <v>-1.706253166666667</v>
       </c>
       <c r="P76">
-        <v>-3.25222172</v>
+        <v>-3.3121385</v>
       </c>
       <c r="Q76">
-        <v>-1.46922172</v>
+        <v>-1.5291385</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3030724819154855</v>
+        <v>0.3133633811921048</v>
       </c>
       <c r="T76">
-        <v>3.35312289427603</v>
+        <v>3.487247810047072</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09061009061009064</v>
+        <v>0.08940195606862276</v>
       </c>
       <c r="W76">
-        <v>0.2144341406341407</v>
+        <v>0.2147190187590187</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2665002665002666</v>
+        <v>0.2629469296135963</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2393801093672903</v>
+        <v>0.2412801093672903</v>
       </c>
       <c r="C77">
-        <v>-13.71642087418012</v>
+        <v>-14.20939247501138</v>
       </c>
       <c r="D77">
-        <v>11.10857912581988</v>
+        <v>11.00060752498862</v>
       </c>
       <c r="E77">
-        <v>10.675</v>
+        <v>11.06</v>
       </c>
       <c r="F77">
-        <v>28.875</v>
+        <v>29.26</v>
       </c>
       <c r="G77">
         <v>4.05</v>
@@ -7601,37 +7601,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M77">
-        <v>6.808725</v>
+        <v>6.899508000000001</v>
       </c>
       <c r="N77">
-        <v>-5.018391666666666</v>
+        <v>-5.109174666666667</v>
       </c>
       <c r="O77">
-        <v>-1.706253166666667</v>
+        <v>-1.737119386666667</v>
       </c>
       <c r="P77">
-        <v>-3.3121385</v>
+        <v>-3.37205528</v>
       </c>
       <c r="Q77">
-        <v>-1.5291385</v>
+        <v>-1.58905528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3133633811921048</v>
+        <v>0.3245118554084426</v>
       </c>
       <c r="T77">
-        <v>3.487247810047072</v>
+        <v>3.632549802132367</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08940195606862276</v>
+        <v>0.08822561454140403</v>
       </c>
       <c r="W77">
-        <v>0.2147190187590187</v>
+        <v>0.2149964000911369</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2629469296135963</v>
+        <v>0.2594871015923648</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2412801093672903</v>
+        <v>0.2431801093672903</v>
       </c>
       <c r="C78">
-        <v>-14.20939247501138</v>
+        <v>-14.700285385723</v>
       </c>
       <c r="D78">
-        <v>11.00060752498862</v>
+        <v>10.894714614277</v>
       </c>
       <c r="E78">
-        <v>11.06</v>
+        <v>11.445</v>
       </c>
       <c r="F78">
-        <v>29.26</v>
+        <v>29.645</v>
       </c>
       <c r="G78">
         <v>4.05</v>
@@ -7683,37 +7683,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M78">
-        <v>6.899508000000001</v>
+        <v>6.990291</v>
       </c>
       <c r="N78">
-        <v>-5.109174666666667</v>
+        <v>-5.199957666666666</v>
       </c>
       <c r="O78">
-        <v>-1.737119386666667</v>
+        <v>-1.767985606666667</v>
       </c>
       <c r="P78">
-        <v>-3.37205528</v>
+        <v>-3.43197206</v>
       </c>
       <c r="Q78">
-        <v>-1.58905528</v>
+        <v>-1.64897206</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3245118554084426</v>
+        <v>0.3366297621653314</v>
       </c>
       <c r="T78">
-        <v>3.632549802132367</v>
+        <v>3.790486750051165</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08822561454140403</v>
+        <v>0.08707982733956762</v>
       </c>
       <c r="W78">
-        <v>0.2149964000911369</v>
+        <v>0.21526657671333</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2594871015923648</v>
+        <v>0.2561171392340225</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2431801093672903</v>
+        <v>0.2450801093672903</v>
       </c>
       <c r="C79">
-        <v>-14.700285385723</v>
+        <v>-15.18915906299489</v>
       </c>
       <c r="D79">
-        <v>10.894714614277</v>
+        <v>10.79084093700511</v>
       </c>
       <c r="E79">
-        <v>11.445</v>
+        <v>11.83</v>
       </c>
       <c r="F79">
-        <v>29.645</v>
+        <v>30.03</v>
       </c>
       <c r="G79">
         <v>4.05</v>
@@ -7765,37 +7765,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M79">
-        <v>6.990291</v>
+        <v>7.081074000000001</v>
       </c>
       <c r="N79">
-        <v>-5.199957666666666</v>
+        <v>-5.290740666666667</v>
       </c>
       <c r="O79">
-        <v>-1.767985606666667</v>
+        <v>-1.798851826666667</v>
       </c>
       <c r="P79">
-        <v>-3.43197206</v>
+        <v>-3.491888840000001</v>
       </c>
       <c r="Q79">
-        <v>-1.64897206</v>
+        <v>-1.70888884</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3366297621653314</v>
+        <v>0.34984929680921</v>
       </c>
       <c r="T79">
-        <v>3.790486750051165</v>
+        <v>3.962781602326217</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08707982733956762</v>
+        <v>0.08596341929675262</v>
       </c>
       <c r="W79">
-        <v>0.21526657671333</v>
+        <v>0.2155298257298257</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2561171392340225</v>
+        <v>0.2528335861669195</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2450801093672903</v>
+        <v>0.2469801093672903</v>
       </c>
       <c r="C80">
-        <v>-15.18915906299489</v>
+        <v>-15.67607071740641</v>
       </c>
       <c r="D80">
-        <v>10.79084093700511</v>
+        <v>10.68892928259359</v>
       </c>
       <c r="E80">
-        <v>11.83</v>
+        <v>12.215</v>
       </c>
       <c r="F80">
-        <v>30.03</v>
+        <v>30.415</v>
       </c>
       <c r="G80">
         <v>4.05</v>
@@ -7847,37 +7847,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M80">
-        <v>7.081074000000001</v>
+        <v>7.171857000000001</v>
       </c>
       <c r="N80">
-        <v>-5.290740666666667</v>
+        <v>-5.381523666666667</v>
       </c>
       <c r="O80">
-        <v>-1.798851826666667</v>
+        <v>-1.829718046666667</v>
       </c>
       <c r="P80">
-        <v>-3.491888840000001</v>
+        <v>-3.551805620000001</v>
       </c>
       <c r="Q80">
-        <v>-1.70888884</v>
+        <v>-1.76880562</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.34984929680921</v>
+        <v>0.3643278347525059</v>
       </c>
       <c r="T80">
-        <v>3.962781602326217</v>
+        <v>4.151485488151277</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08596341929675262</v>
+        <v>0.08487527474869248</v>
       </c>
       <c r="W80">
-        <v>0.2155298257298257</v>
+        <v>0.2157864102142583</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2528335861669195</v>
+        <v>0.2496331610255661</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2469801093672903</v>
+        <v>0.2488801093672903</v>
       </c>
       <c r="C81">
-        <v>-15.67607071740641</v>
+        <v>-16.16107541850787</v>
       </c>
       <c r="D81">
-        <v>10.68892928259359</v>
+        <v>10.58892458149213</v>
       </c>
       <c r="E81">
-        <v>12.215</v>
+        <v>12.6</v>
       </c>
       <c r="F81">
-        <v>30.415</v>
+        <v>30.8</v>
       </c>
       <c r="G81">
         <v>4.05</v>
@@ -7929,37 +7929,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M81">
-        <v>7.171857000000001</v>
+        <v>7.26264</v>
       </c>
       <c r="N81">
-        <v>-5.381523666666667</v>
+        <v>-5.472306666666666</v>
       </c>
       <c r="O81">
-        <v>-1.829718046666667</v>
+        <v>-1.860584266666667</v>
       </c>
       <c r="P81">
-        <v>-3.551805620000001</v>
+        <v>-3.6117224</v>
       </c>
       <c r="Q81">
-        <v>-1.76880562</v>
+        <v>-1.8287224</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3643278347525059</v>
+        <v>0.3802542264901311</v>
       </c>
       <c r="T81">
-        <v>4.151485488151277</v>
+        <v>4.35905976255884</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08487527474869248</v>
+        <v>0.08381433381433383</v>
       </c>
       <c r="W81">
-        <v>0.2157864102142583</v>
+        <v>0.2160365800865801</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2496331610255661</v>
+        <v>0.2465127465127466</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2488801093672903</v>
+        <v>0.2507801093672903</v>
       </c>
       <c r="C82">
-        <v>-16.16107541850787</v>
+        <v>-16.64422619404866</v>
       </c>
       <c r="D82">
-        <v>10.58892458149213</v>
+        <v>10.49077380595135</v>
       </c>
       <c r="E82">
-        <v>12.6</v>
+        <v>12.985</v>
       </c>
       <c r="F82">
-        <v>30.8</v>
+        <v>31.185</v>
       </c>
       <c r="G82">
         <v>4.05</v>
@@ -8011,37 +8011,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M82">
-        <v>7.26264</v>
+        <v>7.353423000000001</v>
       </c>
       <c r="N82">
-        <v>-5.472306666666666</v>
+        <v>-5.563089666666667</v>
       </c>
       <c r="O82">
-        <v>-1.860584266666667</v>
+        <v>-1.891450486666667</v>
       </c>
       <c r="P82">
-        <v>-3.6117224</v>
+        <v>-3.671639180000001</v>
       </c>
       <c r="Q82">
-        <v>-1.8287224</v>
+        <v>-1.88863918</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3802542264901311</v>
+        <v>0.3978570805159276</v>
       </c>
       <c r="T82">
-        <v>4.35905976255884</v>
+        <v>4.588483960588253</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08381433381433383</v>
+        <v>0.08277958895242846</v>
       </c>
       <c r="W82">
-        <v>0.2160365800865801</v>
+        <v>0.2162805729250174</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2465127465127466</v>
+        <v>0.2434693792718484</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2507801093672903</v>
+        <v>0.2526801093672903</v>
       </c>
       <c r="C83">
-        <v>-16.64422619404866</v>
+        <v>-17.12557412373734</v>
       </c>
       <c r="D83">
-        <v>10.49077380595135</v>
+        <v>10.39442587626266</v>
       </c>
       <c r="E83">
-        <v>12.985</v>
+        <v>13.37</v>
       </c>
       <c r="F83">
-        <v>31.185</v>
+        <v>31.57</v>
       </c>
       <c r="G83">
         <v>4.05</v>
@@ -8093,37 +8093,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M83">
-        <v>7.353423000000001</v>
+        <v>7.444206000000001</v>
       </c>
       <c r="N83">
-        <v>-5.563089666666667</v>
+        <v>-5.653872666666667</v>
       </c>
       <c r="O83">
-        <v>-1.891450486666667</v>
+        <v>-1.922316706666667</v>
       </c>
       <c r="P83">
-        <v>-3.671639180000001</v>
+        <v>-3.731555960000001</v>
       </c>
       <c r="Q83">
-        <v>-1.88863918</v>
+        <v>-1.94855596</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3978570805159276</v>
+        <v>0.4174158072112569</v>
       </c>
       <c r="T83">
-        <v>4.588483960588253</v>
+        <v>4.84339973617649</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08277958895242846</v>
+        <v>0.08177008177008177</v>
       </c>
       <c r="W83">
-        <v>0.2162805729250174</v>
+        <v>0.2165186147186147</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2434693792718484</v>
+        <v>0.2405002405002405</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2526801093672903</v>
+        <v>0.2545801093672903</v>
       </c>
       <c r="C84">
-        <v>-17.12557412373734</v>
+        <v>-17.60516842788227</v>
       </c>
       <c r="D84">
-        <v>10.39442587626266</v>
+        <v>10.29983157211774</v>
       </c>
       <c r="E84">
-        <v>13.37</v>
+        <v>13.755</v>
       </c>
       <c r="F84">
-        <v>31.57</v>
+        <v>31.955</v>
       </c>
       <c r="G84">
         <v>4.05</v>
@@ -8175,37 +8175,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M84">
-        <v>7.444206000000001</v>
+        <v>7.534989</v>
       </c>
       <c r="N84">
-        <v>-5.653872666666667</v>
+        <v>-5.744655666666667</v>
       </c>
       <c r="O84">
-        <v>-1.922316706666667</v>
+        <v>-1.953182926666667</v>
       </c>
       <c r="P84">
-        <v>-3.731555960000001</v>
+        <v>-3.79147274</v>
       </c>
       <c r="Q84">
-        <v>-1.94855596</v>
+        <v>-2.008472739999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4174158072112569</v>
+        <v>0.439275560576625</v>
       </c>
       <c r="T84">
-        <v>4.84339973617649</v>
+        <v>5.128305603010402</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08177008177008177</v>
+        <v>0.0807849000620085</v>
       </c>
       <c r="W84">
-        <v>0.2165186147186147</v>
+        <v>0.2167509205653784</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2405002405002405</v>
+        <v>0.2376026472412015</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2545801093672903</v>
+        <v>0.2564801093672903</v>
       </c>
       <c r="C85">
-        <v>-17.60516842788227</v>
+        <v>-18.0830565512357</v>
       </c>
       <c r="D85">
-        <v>10.29983157211774</v>
+        <v>10.2069434487643</v>
       </c>
       <c r="E85">
-        <v>13.755</v>
+        <v>14.14</v>
       </c>
       <c r="F85">
-        <v>31.955</v>
+        <v>32.34</v>
       </c>
       <c r="G85">
         <v>4.05</v>
@@ -8257,37 +8257,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M85">
-        <v>7.534989</v>
+        <v>7.625772000000001</v>
       </c>
       <c r="N85">
-        <v>-5.744655666666667</v>
+        <v>-5.835438666666668</v>
       </c>
       <c r="O85">
-        <v>-1.953182926666667</v>
+        <v>-1.984049146666667</v>
       </c>
       <c r="P85">
-        <v>-3.79147274</v>
+        <v>-3.851389520000001</v>
       </c>
       <c r="Q85">
-        <v>-2.008472739999999</v>
+        <v>-2.06838952</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.439275560576625</v>
+        <v>0.463867783112664</v>
       </c>
       <c r="T85">
-        <v>5.128305603010402</v>
+        <v>5.448824703198552</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0807849000620085</v>
+        <v>0.0798231750612703</v>
       </c>
       <c r="W85">
-        <v>0.2167509205653784</v>
+        <v>0.2169776953205525</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2376026472412015</v>
+        <v>0.2347740442978539</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2564801093672903</v>
+        <v>0.2583801093672903</v>
       </c>
       <c r="C86">
-        <v>-18.08305655123569</v>
+        <v>-18.55928424234176</v>
       </c>
       <c r="D86">
-        <v>10.2069434487643</v>
+        <v>10.11571575765825</v>
       </c>
       <c r="E86">
-        <v>14.14</v>
+        <v>14.525</v>
       </c>
       <c r="F86">
-        <v>32.34</v>
+        <v>32.725</v>
       </c>
       <c r="G86">
         <v>4.05</v>
@@ -8339,37 +8339,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M86">
-        <v>7.625772</v>
+        <v>7.716555</v>
       </c>
       <c r="N86">
-        <v>-5.835438666666666</v>
+        <v>-5.926221666666667</v>
       </c>
       <c r="O86">
-        <v>-1.984049146666667</v>
+        <v>-2.014915366666667</v>
       </c>
       <c r="P86">
-        <v>-3.851389519999999</v>
+        <v>-3.9113063</v>
       </c>
       <c r="Q86">
-        <v>-2.068389519999999</v>
+        <v>-2.128306299999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4638677831126638</v>
+        <v>0.491738968653508</v>
       </c>
       <c r="T86">
-        <v>5.448824703198549</v>
+        <v>5.812079683411786</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07982317506127032</v>
+        <v>0.07888407888407889</v>
       </c>
       <c r="W86">
-        <v>0.2169776953205525</v>
+        <v>0.2171991341991342</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2347740442978539</v>
+        <v>0.2320119967178791</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2583801093672903</v>
+        <v>0.2602801093672903</v>
       </c>
       <c r="C87">
-        <v>-18.55928424234176</v>
+        <v>-19.0338956286668</v>
       </c>
       <c r="D87">
-        <v>10.11571575765825</v>
+        <v>10.0261043713332</v>
       </c>
       <c r="E87">
-        <v>14.525</v>
+        <v>14.91</v>
       </c>
       <c r="F87">
-        <v>32.725</v>
+        <v>33.11</v>
       </c>
       <c r="G87">
         <v>4.05</v>
@@ -8421,37 +8421,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M87">
-        <v>7.716555</v>
+        <v>7.807338000000001</v>
       </c>
       <c r="N87">
-        <v>-5.926221666666667</v>
+        <v>-6.017004666666667</v>
       </c>
       <c r="O87">
-        <v>-2.014915366666667</v>
+        <v>-2.045781586666667</v>
       </c>
       <c r="P87">
-        <v>-3.9113063</v>
+        <v>-3.97122308</v>
       </c>
       <c r="Q87">
-        <v>-2.128306299999999</v>
+        <v>-2.18822308</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.491738968653508</v>
+        <v>0.5235917521287586</v>
       </c>
       <c r="T87">
-        <v>5.812079683411786</v>
+        <v>6.227228232226913</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07888407888407889</v>
+        <v>0.07796682215286868</v>
       </c>
       <c r="W87">
-        <v>0.2171991341991342</v>
+        <v>0.2174154233363536</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2320119967178791</v>
+        <v>0.2293141828025549</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2602801093672903</v>
+        <v>0.2621801093672902</v>
       </c>
       <c r="C88">
-        <v>-19.0338956286668</v>
+        <v>-19.50693328777158</v>
       </c>
       <c r="D88">
-        <v>10.0261043713332</v>
+        <v>9.938066712228414</v>
       </c>
       <c r="E88">
-        <v>14.91</v>
+        <v>15.295</v>
       </c>
       <c r="F88">
-        <v>33.11</v>
+        <v>33.495</v>
       </c>
       <c r="G88">
         <v>4.05</v>
@@ -8503,37 +8503,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M88">
-        <v>7.807338000000001</v>
+        <v>7.898121</v>
       </c>
       <c r="N88">
-        <v>-6.017004666666667</v>
+        <v>-6.107787666666666</v>
       </c>
       <c r="O88">
-        <v>-2.045781586666667</v>
+        <v>-2.076647806666667</v>
       </c>
       <c r="P88">
-        <v>-3.97122308</v>
+        <v>-4.03113986</v>
       </c>
       <c r="Q88">
-        <v>-2.18822308</v>
+        <v>-2.248139859999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5235917521287586</v>
+        <v>0.5603449638309708</v>
       </c>
       <c r="T88">
-        <v>6.227228232226913</v>
+        <v>6.70624578855206</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07796682215286868</v>
+        <v>0.07707065178329547</v>
       </c>
       <c r="W88">
-        <v>0.2174154233363536</v>
+        <v>0.2176267403094989</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2293141828025549</v>
+        <v>0.2266783875979279</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2621801093672902</v>
+        <v>0.2640801093672903</v>
       </c>
       <c r="C89">
-        <v>-19.50693328777158</v>
+        <v>-19.97843831476634</v>
       </c>
       <c r="D89">
-        <v>9.938066712228414</v>
+        <v>9.851561685233664</v>
       </c>
       <c r="E89">
-        <v>15.295</v>
+        <v>15.68</v>
       </c>
       <c r="F89">
-        <v>33.495</v>
+        <v>33.88</v>
       </c>
       <c r="G89">
         <v>4.05</v>
@@ -8585,37 +8585,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M89">
-        <v>7.898121</v>
+        <v>7.988904000000001</v>
       </c>
       <c r="N89">
-        <v>-6.107787666666666</v>
+        <v>-6.198570666666667</v>
       </c>
       <c r="O89">
-        <v>-2.076647806666667</v>
+        <v>-2.107514026666667</v>
       </c>
       <c r="P89">
-        <v>-4.03113986</v>
+        <v>-4.09105664</v>
       </c>
       <c r="Q89">
-        <v>-2.248139859999999</v>
+        <v>-2.308056639999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5603449638309708</v>
+        <v>0.6032237108168851</v>
       </c>
       <c r="T89">
-        <v>6.70624578855206</v>
+        <v>7.265099604264734</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07707065178329547</v>
+        <v>0.07619484892212167</v>
       </c>
       <c r="W89">
-        <v>0.2176267403094989</v>
+        <v>0.2178332546241637</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2266783875979279</v>
+        <v>0.2241024968297696</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2640801093672903</v>
+        <v>0.2659801093672903</v>
       </c>
       <c r="C90">
-        <v>-19.97843831476634</v>
+        <v>-20.4484503862733</v>
       </c>
       <c r="D90">
-        <v>9.851561685233664</v>
+        <v>9.766549613726697</v>
       </c>
       <c r="E90">
-        <v>15.68</v>
+        <v>16.065</v>
       </c>
       <c r="F90">
-        <v>33.88</v>
+        <v>34.265</v>
       </c>
       <c r="G90">
         <v>4.05</v>
@@ -8667,37 +8667,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M90">
-        <v>7.988904000000001</v>
+        <v>8.079687</v>
       </c>
       <c r="N90">
-        <v>-6.198570666666667</v>
+        <v>-6.289353666666666</v>
       </c>
       <c r="O90">
-        <v>-2.107514026666667</v>
+        <v>-2.138380246666667</v>
       </c>
       <c r="P90">
-        <v>-4.09105664</v>
+        <v>-4.15097342</v>
       </c>
       <c r="Q90">
-        <v>-2.308056639999999</v>
+        <v>-2.367973419999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6032237108168851</v>
+        <v>0.6538985936184202</v>
       </c>
       <c r="T90">
-        <v>7.265099604264734</v>
+        <v>7.925563204652437</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07619484892212167</v>
+        <v>0.0753387270241203</v>
       </c>
       <c r="W90">
-        <v>0.2178332546241637</v>
+        <v>0.2180351281677124</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2241024968297696</v>
+        <v>0.2215844912474126</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2659801093672903</v>
+        <v>0.2678801093672902</v>
       </c>
       <c r="C91">
-        <v>-20.4484503862733</v>
+        <v>-20.91700782110593</v>
       </c>
       <c r="D91">
-        <v>9.766549613726697</v>
+        <v>9.682992178894072</v>
       </c>
       <c r="E91">
-        <v>16.065</v>
+        <v>16.45</v>
       </c>
       <c r="F91">
-        <v>34.265</v>
+        <v>34.65</v>
       </c>
       <c r="G91">
         <v>4.05</v>
@@ -8749,37 +8749,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M91">
-        <v>8.079687</v>
+        <v>8.17047</v>
       </c>
       <c r="N91">
-        <v>-6.289353666666666</v>
+        <v>-6.380136666666666</v>
       </c>
       <c r="O91">
-        <v>-2.138380246666667</v>
+        <v>-2.169246466666666</v>
       </c>
       <c r="P91">
-        <v>-4.15097342</v>
+        <v>-4.2108902</v>
       </c>
       <c r="Q91">
-        <v>-2.367973419999999</v>
+        <v>-2.427890199999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6538985936184202</v>
+        <v>0.7147084529802621</v>
       </c>
       <c r="T91">
-        <v>7.925563204652437</v>
+        <v>8.718119525117679</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0753387270241203</v>
+        <v>0.07450163005718563</v>
       </c>
       <c r="W91">
-        <v>0.2180351281677124</v>
+        <v>0.2182325156325156</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2215844912474126</v>
+        <v>0.2191224413446636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2678801093672902</v>
+        <v>0.2697801093672903</v>
       </c>
       <c r="C92">
-        <v>-20.91700782110593</v>
+        <v>-21.38414763785962</v>
       </c>
       <c r="D92">
-        <v>9.682992178894072</v>
+        <v>9.600852362140387</v>
       </c>
       <c r="E92">
-        <v>16.45</v>
+        <v>16.835</v>
       </c>
       <c r="F92">
-        <v>34.65</v>
+        <v>35.035</v>
       </c>
       <c r="G92">
         <v>4.05</v>
@@ -8831,37 +8831,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M92">
-        <v>8.17047</v>
+        <v>8.261253000000002</v>
       </c>
       <c r="N92">
-        <v>-6.380136666666666</v>
+        <v>-6.470919666666668</v>
       </c>
       <c r="O92">
-        <v>-2.169246466666666</v>
+        <v>-2.200112686666667</v>
       </c>
       <c r="P92">
-        <v>-4.2108902</v>
+        <v>-4.270806980000001</v>
       </c>
       <c r="Q92">
-        <v>-2.427890199999999</v>
+        <v>-2.48780698</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7147084529802621</v>
+        <v>0.7890316144225137</v>
       </c>
       <c r="T92">
-        <v>8.718119525117679</v>
+        <v>9.68679947235298</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07450163005718563</v>
+        <v>0.07368293082578796</v>
       </c>
       <c r="W92">
-        <v>0.2182325156325156</v>
+        <v>0.2184255649112792</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2191224413446636</v>
+        <v>0.2167145024287882</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2697801093672903</v>
+        <v>0.2716801093672903</v>
       </c>
       <c r="C93">
-        <v>-21.38414763785962</v>
+        <v>-21.84990560959588</v>
       </c>
       <c r="D93">
-        <v>9.600852362140387</v>
+        <v>9.520094390404127</v>
       </c>
       <c r="E93">
-        <v>16.835</v>
+        <v>17.22</v>
       </c>
       <c r="F93">
-        <v>35.035</v>
+        <v>35.42</v>
       </c>
       <c r="G93">
         <v>4.05</v>
@@ -8913,37 +8913,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M93">
-        <v>8.261253000000002</v>
+        <v>8.352036</v>
       </c>
       <c r="N93">
-        <v>-6.470919666666668</v>
+        <v>-6.561702666666666</v>
       </c>
       <c r="O93">
-        <v>-2.200112686666667</v>
+        <v>-2.230978906666667</v>
       </c>
       <c r="P93">
-        <v>-4.270806980000001</v>
+        <v>-4.33072376</v>
       </c>
       <c r="Q93">
-        <v>-2.48780698</v>
+        <v>-2.547723759999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7890316144225137</v>
+        <v>0.8819355662253281</v>
       </c>
       <c r="T93">
-        <v>9.68679947235298</v>
+        <v>10.89764940639711</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07368293082578796</v>
+        <v>0.07288202940376855</v>
       </c>
       <c r="W93">
-        <v>0.2184255649112792</v>
+        <v>0.2186144174665914</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2167145024287882</v>
+        <v>0.214358910011084</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2716801093672903</v>
+        <v>0.2735801093672903</v>
       </c>
       <c r="C94">
-        <v>-21.84990560959588</v>
+        <v>-22.31431631578972</v>
       </c>
       <c r="D94">
-        <v>9.520094390404127</v>
+        <v>9.440683684210283</v>
       </c>
       <c r="E94">
-        <v>17.22</v>
+        <v>17.605</v>
       </c>
       <c r="F94">
-        <v>35.42</v>
+        <v>35.805</v>
       </c>
       <c r="G94">
         <v>4.05</v>
@@ -8995,37 +8995,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M94">
-        <v>8.352036</v>
+        <v>8.442819</v>
       </c>
       <c r="N94">
-        <v>-6.561702666666666</v>
+        <v>-6.652485666666666</v>
       </c>
       <c r="O94">
-        <v>-2.230978906666667</v>
+        <v>-2.261845126666667</v>
       </c>
       <c r="P94">
-        <v>-4.33072376</v>
+        <v>-4.39064054</v>
       </c>
       <c r="Q94">
-        <v>-2.547723759999999</v>
+        <v>-2.607640539999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8819355662253281</v>
+        <v>1.001383504257518</v>
       </c>
       <c r="T94">
-        <v>10.89764940639711</v>
+        <v>12.45445646445384</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07288202940376855</v>
+        <v>0.07209835166824416</v>
       </c>
       <c r="W94">
-        <v>0.2186144174665914</v>
+        <v>0.218799208676628</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.214358910011084</v>
+        <v>0.2120539754948357</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2735801093672903</v>
+        <v>0.2754801093672903</v>
       </c>
       <c r="C95">
-        <v>-22.31431631578972</v>
+        <v>-22.77741319169862</v>
       </c>
       <c r="D95">
-        <v>9.440683684210283</v>
+        <v>9.362586808301382</v>
       </c>
       <c r="E95">
-        <v>17.605</v>
+        <v>17.99000000000001</v>
       </c>
       <c r="F95">
-        <v>35.805</v>
+        <v>36.19</v>
       </c>
       <c r="G95">
         <v>4.05</v>
@@ -9077,37 +9077,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M95">
-        <v>8.442819</v>
+        <v>8.533602000000002</v>
       </c>
       <c r="N95">
-        <v>-6.652485666666666</v>
+        <v>-6.743268666666668</v>
       </c>
       <c r="O95">
-        <v>-2.261845126666667</v>
+        <v>-2.292711346666668</v>
       </c>
       <c r="P95">
-        <v>-4.39064054</v>
+        <v>-4.450557320000001</v>
       </c>
       <c r="Q95">
-        <v>-2.607640539999999</v>
+        <v>-2.66755732</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.001383504257518</v>
+        <v>1.160647421633771</v>
       </c>
       <c r="T95">
-        <v>12.45445646445384</v>
+        <v>14.53019920852948</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07209835166824416</v>
+        <v>0.0713313479270926</v>
       </c>
       <c r="W95">
-        <v>0.218799208676628</v>
+        <v>0.2189800681587916</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2120539754948357</v>
+        <v>0.2097980821385077</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2754801093672903</v>
+        <v>0.2773801093672903</v>
       </c>
       <c r="C96">
-        <v>-22.77741319169862</v>
+        <v>-23.23922857530119</v>
       </c>
       <c r="D96">
-        <v>9.362586808301382</v>
+        <v>9.285771424698817</v>
       </c>
       <c r="E96">
-        <v>17.99000000000001</v>
+        <v>18.375</v>
       </c>
       <c r="F96">
-        <v>36.19</v>
+        <v>36.575</v>
       </c>
       <c r="G96">
         <v>4.05</v>
@@ -9159,37 +9159,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M96">
-        <v>8.533602000000002</v>
+        <v>8.624385</v>
       </c>
       <c r="N96">
-        <v>-6.743268666666668</v>
+        <v>-6.834051666666666</v>
       </c>
       <c r="O96">
-        <v>-2.292711346666668</v>
+        <v>-2.323577566666667</v>
       </c>
       <c r="P96">
-        <v>-4.450557320000001</v>
+        <v>-4.5104741</v>
       </c>
       <c r="Q96">
-        <v>-2.66755732</v>
+        <v>-2.727474099999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.160647421633771</v>
+        <v>1.383616905960526</v>
       </c>
       <c r="T96">
-        <v>14.53019920852948</v>
+        <v>17.43623905023538</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0713313479270926</v>
+        <v>0.07058049163312323</v>
       </c>
       <c r="W96">
-        <v>0.2189800681587916</v>
+        <v>0.2191571200729096</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2097980821385077</v>
+        <v>0.2075896812738919</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2773801093672903</v>
+        <v>0.2792801093672903</v>
       </c>
       <c r="C97">
-        <v>-23.23922857530119</v>
+        <v>-23.69979375194402</v>
       </c>
       <c r="D97">
-        <v>9.285771424698817</v>
+        <v>9.210206248055981</v>
       </c>
       <c r="E97">
-        <v>18.375</v>
+        <v>18.76</v>
       </c>
       <c r="F97">
-        <v>36.575</v>
+        <v>36.96</v>
       </c>
       <c r="G97">
         <v>4.05</v>
@@ -9241,37 +9241,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M97">
-        <v>8.624385</v>
+        <v>8.715168</v>
       </c>
       <c r="N97">
-        <v>-6.834051666666666</v>
+        <v>-6.924834666666666</v>
       </c>
       <c r="O97">
-        <v>-2.323577566666667</v>
+        <v>-2.354443786666667</v>
       </c>
       <c r="P97">
-        <v>-4.5104741</v>
+        <v>-4.57039088</v>
       </c>
       <c r="Q97">
-        <v>-2.727474099999999</v>
+        <v>-2.787390879999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.383616905960526</v>
+        <v>1.718071132450659</v>
       </c>
       <c r="T97">
-        <v>17.43623905023538</v>
+        <v>21.79529881279424</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07058049163312323</v>
+        <v>0.06984527817861153</v>
       </c>
       <c r="W97">
-        <v>0.2191571200729096</v>
+        <v>0.2193304834054834</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2075896812738919</v>
+        <v>0.2054272887606221</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2792801093672903</v>
+        <v>0.2811801093672903</v>
       </c>
       <c r="C98">
-        <v>-23.69979375194402</v>
+        <v>-24.1591389968262</v>
       </c>
       <c r="D98">
-        <v>9.210206248055981</v>
+        <v>9.135861003173797</v>
       </c>
       <c r="E98">
-        <v>18.76</v>
+        <v>19.145</v>
       </c>
       <c r="F98">
-        <v>36.96</v>
+        <v>37.345</v>
       </c>
       <c r="G98">
         <v>4.05</v>
@@ -9323,37 +9323,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M98">
-        <v>8.715168</v>
+        <v>8.805951</v>
       </c>
       <c r="N98">
-        <v>-6.924834666666666</v>
+        <v>-7.015617666666667</v>
       </c>
       <c r="O98">
-        <v>-2.354443786666667</v>
+        <v>-2.385310006666667</v>
       </c>
       <c r="P98">
-        <v>-4.57039088</v>
+        <v>-4.63030766</v>
       </c>
       <c r="Q98">
-        <v>-2.787390879999999</v>
+        <v>-2.847307659999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.718071132450654</v>
+        <v>2.275494843267539</v>
       </c>
       <c r="T98">
-        <v>21.79529881279418</v>
+        <v>29.06039841705891</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06984527817861153</v>
+        <v>0.06912522376439904</v>
       </c>
       <c r="W98">
-        <v>0.2193304834054834</v>
+        <v>0.2195002722363547</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2054272887606221</v>
+        <v>0.2033094816599972</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2811801093672903</v>
+        <v>0.2830801093672903</v>
       </c>
       <c r="C99">
-        <v>-24.1591389968262</v>
+        <v>-24.61729361544263</v>
       </c>
       <c r="D99">
-        <v>9.135861003173797</v>
+        <v>9.062706384557362</v>
       </c>
       <c r="E99">
-        <v>19.145</v>
+        <v>19.53</v>
       </c>
       <c r="F99">
-        <v>37.345</v>
+        <v>37.73</v>
       </c>
       <c r="G99">
         <v>4.05</v>
@@ -9405,37 +9405,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M99">
-        <v>8.805951</v>
+        <v>8.896734</v>
       </c>
       <c r="N99">
-        <v>-7.015617666666667</v>
+        <v>-7.106400666666667</v>
       </c>
       <c r="O99">
-        <v>-2.385310006666667</v>
+        <v>-2.416176226666667</v>
       </c>
       <c r="P99">
-        <v>-4.63030766</v>
+        <v>-4.69022444</v>
       </c>
       <c r="Q99">
-        <v>-2.847307659999999</v>
+        <v>-2.907224439999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.275494843267539</v>
+        <v>3.390342264901308</v>
       </c>
       <c r="T99">
-        <v>29.06039841705891</v>
+        <v>43.59059762558836</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06912522376439904</v>
+        <v>0.0684198643382317</v>
       </c>
       <c r="W99">
-        <v>0.2195002722363547</v>
+        <v>0.219666595989045</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2033094816599972</v>
+        <v>0.2012348951124462</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2830801093672903</v>
+        <v>0.2849801093672903</v>
       </c>
       <c r="C100">
-        <v>-24.61729361544263</v>
+        <v>-25.07428598209976</v>
       </c>
       <c r="D100">
-        <v>9.062706384557362</v>
+        <v>8.990714017900247</v>
       </c>
       <c r="E100">
-        <v>19.53</v>
+        <v>19.915</v>
       </c>
       <c r="F100">
-        <v>37.73</v>
+        <v>38.115</v>
       </c>
       <c r="G100">
         <v>4.05</v>
@@ -9487,37 +9487,37 @@
         <v>1.790333333333334</v>
       </c>
       <c r="M100">
-        <v>8.896734</v>
+        <v>8.987517</v>
       </c>
       <c r="N100">
-        <v>-7.106400666666667</v>
+        <v>-7.197183666666667</v>
       </c>
       <c r="O100">
-        <v>-2.416176226666667</v>
+        <v>-2.447042446666667</v>
       </c>
       <c r="P100">
-        <v>-4.69022444</v>
+        <v>-4.75014122</v>
       </c>
       <c r="Q100">
-        <v>-2.907224439999999</v>
+        <v>-2.967141219999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.390342264901308</v>
+        <v>6.734884529802615</v>
       </c>
       <c r="T100">
-        <v>43.59059762558836</v>
+        <v>87.18119525117672</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0684198643382317</v>
+        <v>0.06772875459744147</v>
       </c>
       <c r="W100">
-        <v>0.219666595989045</v>
+        <v>0.2198295596659233</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2012348951124462</v>
+        <v>0.1992022194042397</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2849801093672903</v>
-      </c>
-      <c r="C101">
-        <v>-25.07428598209976</v>
-      </c>
-      <c r="D101">
-        <v>8.990714017900247</v>
-      </c>
-      <c r="E101">
-        <v>19.915</v>
-      </c>
-      <c r="F101">
-        <v>38.115</v>
-      </c>
-      <c r="G101">
-        <v>4.05</v>
-      </c>
-      <c r="H101">
-        <v>20.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.573333333333334</v>
-      </c>
-      <c r="K101">
-        <v>1.783</v>
-      </c>
-      <c r="L101">
-        <v>1.790333333333334</v>
-      </c>
-      <c r="M101">
-        <v>8.987517</v>
-      </c>
-      <c r="N101">
-        <v>-7.197183666666667</v>
-      </c>
-      <c r="O101">
-        <v>-2.447042446666667</v>
-      </c>
-      <c r="P101">
-        <v>-4.75014122</v>
-      </c>
-      <c r="Q101">
-        <v>-2.967141219999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.734884529802615</v>
-      </c>
-      <c r="T101">
-        <v>87.18119525117672</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06772875459744147</v>
-      </c>
-      <c r="W101">
-        <v>0.2198295596659233</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1992022194042397</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
